--- a/业绩表/业绩表.xlsx
+++ b/业绩表/业绩表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github本地\github\业绩表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{907B1281-8632-409E-8045-C5A6FEF53673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CC487F-66A2-46C7-9F9B-A8368762A997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8940" yWindow="930" windowWidth="19095" windowHeight="12030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="423">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="425">
   <si>
     <t>姓名</t>
   </si>
@@ -1630,6 +1630,14 @@
   </si>
   <si>
     <t>SF5121267075268</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙血树叶*10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>吴</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2101,6 +2109,27 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2120,27 +2149,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2695,48 +2703,48 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="48" t="s">
         <v>369</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="57" t="s">
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="50" t="s">
         <v>370</v>
       </c>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="59"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="52"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
     <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="46">
+      <c r="A3" s="53">
         <v>45748</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="48"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="54"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="54"/>
+      <c r="I3" s="54"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="54"/>
+      <c r="L3" s="54"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="55"/>
     </row>
     <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -2830,23 +2838,23 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="46">
+      <c r="A6" s="53">
         <v>45778</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="48"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="54"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="54"/>
+      <c r="O6" s="55"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="22"/>
     </row>
@@ -3178,19 +3186,19 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="50"/>
+      <c r="H14" s="57"/>
       <c r="I14" s="6">
         <f>SUM(I7:I13)</f>
         <v>32768</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="52"/>
+      <c r="L14" s="59"/>
       <c r="M14" s="7">
         <f>SUM(N7:N13)</f>
         <v>6500</v>
@@ -3206,23 +3214,23 @@
       <c r="Q14" s="22"/>
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="46">
+      <c r="A15" s="53">
         <v>45809</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="48"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="54"/>
+      <c r="I15" s="54"/>
+      <c r="J15" s="54"/>
+      <c r="K15" s="54"/>
+      <c r="L15" s="54"/>
+      <c r="M15" s="54"/>
+      <c r="N15" s="54"/>
+      <c r="O15" s="55"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="22"/>
     </row>
@@ -3675,19 +3683,19 @@
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="49" t="s">
+      <c r="G26" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="50"/>
+      <c r="H26" s="57"/>
       <c r="I26" s="6">
         <f>SUM(I16:I25)</f>
         <v>47760</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="51" t="s">
+      <c r="K26" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="52"/>
+      <c r="L26" s="59"/>
       <c r="M26" s="7">
         <f>SUM(N18:N25)</f>
         <v>0</v>
@@ -3701,23 +3709,23 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="46">
+      <c r="A27" s="53">
         <v>45839</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="48"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="55"/>
     </row>
     <row r="28" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
@@ -4347,19 +4355,19 @@
         <f>G33+G35+G37+G40</f>
         <v>0</v>
       </c>
-      <c r="G42" s="49" t="s">
+      <c r="G42" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="50"/>
+      <c r="H42" s="57"/>
       <c r="I42" s="6">
         <f>SUM(I28:I41)</f>
         <v>52960</v>
       </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="51" t="s">
+      <c r="K42" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="52"/>
+      <c r="L42" s="59"/>
       <c r="M42" s="7">
         <f>SUM(N28:N41)</f>
         <v>18470</v>
@@ -4373,23 +4381,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="46">
+      <c r="A43" s="53">
         <v>45870</v>
       </c>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="47"/>
-      <c r="M43" s="47"/>
-      <c r="N43" s="47"/>
-      <c r="O43" s="48"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="54"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="54"/>
+      <c r="F43" s="54"/>
+      <c r="G43" s="54"/>
+      <c r="H43" s="54"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="54"/>
+      <c r="K43" s="54"/>
+      <c r="L43" s="54"/>
+      <c r="M43" s="54"/>
+      <c r="N43" s="54"/>
+      <c r="O43" s="55"/>
     </row>
     <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="36" t="s">
@@ -4577,19 +4585,19 @@
         <f>G46+G47</f>
         <v>585</v>
       </c>
-      <c r="G48" s="49" t="s">
+      <c r="G48" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="50"/>
+      <c r="H48" s="57"/>
       <c r="I48" s="6">
         <f>SUM(I44:I47)</f>
         <v>11470</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="51" t="s">
+      <c r="K48" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L48" s="52"/>
+      <c r="L48" s="59"/>
       <c r="M48" s="7">
         <f>SUM(N44:N47)</f>
         <v>2985</v>
@@ -4603,23 +4611,23 @@
       </c>
     </row>
     <row r="49" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="46">
+      <c r="A49" s="53">
         <v>45901</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
-      <c r="M49" s="47"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="48"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="54"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="54"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="54"/>
+      <c r="H49" s="54"/>
+      <c r="I49" s="54"/>
+      <c r="J49" s="54"/>
+      <c r="K49" s="54"/>
+      <c r="L49" s="54"/>
+      <c r="M49" s="54"/>
+      <c r="N49" s="54"/>
+      <c r="O49" s="55"/>
     </row>
     <row r="50" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
@@ -4992,19 +5000,19 @@
         <f>SUM(G51:G57)</f>
         <v>438</v>
       </c>
-      <c r="G58" s="49" t="s">
+      <c r="G58" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="50"/>
+      <c r="H58" s="57"/>
       <c r="I58" s="6">
         <f>SUM(I50:I57)</f>
         <v>35689</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="51" t="s">
+      <c r="K58" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L58" s="52"/>
+      <c r="L58" s="59"/>
       <c r="M58" s="7">
         <f>SUM(N50:N57)</f>
         <v>4186</v>
@@ -5018,23 +5026,23 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="46">
+      <c r="A59" s="53">
         <v>45931</v>
       </c>
-      <c r="B59" s="47"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="47"/>
-      <c r="H59" s="47"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
-      <c r="M59" s="47"/>
-      <c r="N59" s="47"/>
-      <c r="O59" s="48"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="54"/>
+      <c r="I59" s="54"/>
+      <c r="J59" s="54"/>
+      <c r="K59" s="54"/>
+      <c r="L59" s="54"/>
+      <c r="M59" s="54"/>
+      <c r="N59" s="54"/>
+      <c r="O59" s="55"/>
     </row>
     <row r="60" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
@@ -5357,19 +5365,19 @@
         <f>SUM(G60:G66)</f>
         <v>640</v>
       </c>
-      <c r="G67" s="49" t="s">
+      <c r="G67" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="50"/>
+      <c r="H67" s="57"/>
       <c r="I67" s="6">
         <f>SUM(I60:I66)</f>
         <v>26988</v>
       </c>
       <c r="J67" s="5"/>
-      <c r="K67" s="51" t="s">
+      <c r="K67" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L67" s="52"/>
+      <c r="L67" s="59"/>
       <c r="M67" s="7">
         <f>SUM(N57:N66)</f>
         <v>0</v>
@@ -5383,23 +5391,23 @@
       </c>
     </row>
     <row r="68" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="46">
+      <c r="A68" s="53">
         <v>45962</v>
       </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="47"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="47"/>
-      <c r="J68" s="47"/>
-      <c r="K68" s="47"/>
-      <c r="L68" s="47"/>
-      <c r="M68" s="47"/>
-      <c r="N68" s="47"/>
-      <c r="O68" s="48"/>
+      <c r="B68" s="54"/>
+      <c r="C68" s="54"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="54"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="54"/>
+      <c r="H68" s="54"/>
+      <c r="I68" s="54"/>
+      <c r="J68" s="54"/>
+      <c r="K68" s="54"/>
+      <c r="L68" s="54"/>
+      <c r="M68" s="54"/>
+      <c r="N68" s="54"/>
+      <c r="O68" s="55"/>
     </row>
     <row r="69" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
@@ -6215,19 +6223,19 @@
         <f>SUM(G69:G80)</f>
         <v>3062</v>
       </c>
-      <c r="G87" s="49" t="s">
+      <c r="G87" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H87" s="50"/>
+      <c r="H87" s="57"/>
       <c r="I87" s="6">
         <f>SUM(I69:I86)</f>
         <v>123444</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="51" t="s">
+      <c r="K87" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L87" s="52"/>
+      <c r="L87" s="59"/>
       <c r="M87" s="7">
         <f>SUM(N69:N85)</f>
         <v>87602</v>
@@ -6241,23 +6249,23 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="46">
+      <c r="A88" s="53">
         <v>45992</v>
       </c>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
-      <c r="J88" s="47"/>
-      <c r="K88" s="47"/>
-      <c r="L88" s="47"/>
-      <c r="M88" s="47"/>
-      <c r="N88" s="47"/>
-      <c r="O88" s="48"/>
+      <c r="B88" s="54"/>
+      <c r="C88" s="54"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="54"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="54"/>
+      <c r="H88" s="54"/>
+      <c r="I88" s="54"/>
+      <c r="J88" s="54"/>
+      <c r="K88" s="54"/>
+      <c r="L88" s="54"/>
+      <c r="M88" s="54"/>
+      <c r="N88" s="54"/>
+      <c r="O88" s="55"/>
     </row>
     <row r="89" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
@@ -6620,19 +6628,19 @@
         <f>SUM(G76:G87)</f>
         <v>4470</v>
       </c>
-      <c r="G97" s="49" t="s">
+      <c r="G97" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="50"/>
+      <c r="H97" s="57"/>
       <c r="I97" s="6">
         <f>SUM(I89:I96)</f>
         <v>27632</v>
       </c>
       <c r="J97" s="5"/>
-      <c r="K97" s="51" t="s">
+      <c r="K97" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L97" s="52"/>
+      <c r="L97" s="59"/>
       <c r="M97" s="7">
         <f>SUM(N89:N94)</f>
         <v>0</v>
@@ -6646,23 +6654,23 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="46">
+      <c r="A98" s="53">
         <v>46023</v>
       </c>
-      <c r="B98" s="47"/>
-      <c r="C98" s="47"/>
-      <c r="D98" s="47"/>
-      <c r="E98" s="47"/>
-      <c r="F98" s="47"/>
-      <c r="G98" s="47"/>
-      <c r="H98" s="47"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="47"/>
-      <c r="K98" s="47"/>
-      <c r="L98" s="47"/>
-      <c r="M98" s="47"/>
-      <c r="N98" s="47"/>
-      <c r="O98" s="48"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="54"/>
+      <c r="H98" s="54"/>
+      <c r="I98" s="54"/>
+      <c r="J98" s="54"/>
+      <c r="K98" s="54"/>
+      <c r="L98" s="54"/>
+      <c r="M98" s="54"/>
+      <c r="N98" s="54"/>
+      <c r="O98" s="55"/>
     </row>
     <row r="99" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="38" t="s">
@@ -7247,7 +7255,9 @@
       <c r="M111" s="43" t="s">
         <v>397</v>
       </c>
-      <c r="N111" s="17"/>
+      <c r="N111" s="45" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="112" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="1" t="s">
@@ -7684,19 +7694,19 @@
         <f>SUM(G106:G117)</f>
         <v>2483</v>
       </c>
-      <c r="G122" s="49" t="s">
+      <c r="G122" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H122" s="50"/>
+      <c r="H122" s="57"/>
       <c r="I122" s="6">
         <f>SUM(I99:I121)</f>
         <v>53972</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="51" t="s">
+      <c r="K122" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L122" s="52"/>
+      <c r="L122" s="59"/>
       <c r="M122" s="7">
         <f>SUM(N99:N121)</f>
         <v>30730</v>
@@ -7710,23 +7720,23 @@
       </c>
     </row>
     <row r="123" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="46">
+      <c r="A123" s="53">
         <v>46054</v>
       </c>
-      <c r="B123" s="47"/>
-      <c r="C123" s="47"/>
-      <c r="D123" s="47"/>
-      <c r="E123" s="47"/>
-      <c r="F123" s="47"/>
-      <c r="G123" s="47"/>
-      <c r="H123" s="47"/>
-      <c r="I123" s="47"/>
-      <c r="J123" s="47"/>
-      <c r="K123" s="47"/>
-      <c r="L123" s="47"/>
-      <c r="M123" s="47"/>
-      <c r="N123" s="47"/>
-      <c r="O123" s="48"/>
+      <c r="B123" s="54"/>
+      <c r="C123" s="54"/>
+      <c r="D123" s="54"/>
+      <c r="E123" s="54"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="54"/>
+      <c r="H123" s="54"/>
+      <c r="I123" s="54"/>
+      <c r="J123" s="54"/>
+      <c r="K123" s="54"/>
+      <c r="L123" s="54"/>
+      <c r="M123" s="54"/>
+      <c r="N123" s="54"/>
+      <c r="O123" s="55"/>
     </row>
     <row r="124" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
@@ -7866,19 +7876,19 @@
         <f>SUM(G110:G121)</f>
         <v>2121</v>
       </c>
-      <c r="G127" s="49" t="s">
+      <c r="G127" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="50"/>
+      <c r="H127" s="57"/>
       <c r="I127" s="6">
         <f>SUM(I124:I126)</f>
         <v>6587</v>
       </c>
       <c r="J127" s="5"/>
-      <c r="K127" s="51" t="s">
+      <c r="K127" s="58" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="52"/>
+      <c r="L127" s="59"/>
       <c r="M127" s="7">
         <f>SUM(N124:N125)</f>
         <v>0</v>
@@ -7892,23 +7902,23 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="46">
+      <c r="A128" s="53">
         <v>46082</v>
       </c>
-      <c r="B128" s="47"/>
-      <c r="C128" s="47"/>
-      <c r="D128" s="47"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="47"/>
-      <c r="G128" s="47"/>
-      <c r="H128" s="47"/>
-      <c r="I128" s="47"/>
-      <c r="J128" s="47"/>
-      <c r="K128" s="47"/>
-      <c r="L128" s="47"/>
-      <c r="M128" s="47"/>
-      <c r="N128" s="47"/>
-      <c r="O128" s="48"/>
+      <c r="B128" s="54"/>
+      <c r="C128" s="54"/>
+      <c r="D128" s="54"/>
+      <c r="E128" s="54"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="54"/>
+      <c r="H128" s="54"/>
+      <c r="I128" s="54"/>
+      <c r="J128" s="54"/>
+      <c r="K128" s="54"/>
+      <c r="L128" s="54"/>
+      <c r="M128" s="54"/>
+      <c r="N128" s="54"/>
+      <c r="O128" s="55"/>
     </row>
     <row r="129" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
@@ -7984,7 +7994,7 @@
         <v>59</v>
       </c>
       <c r="K130" s="1" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="L130" s="2">
         <v>3.4</v>
@@ -7995,7 +8005,43 @@
       <c r="N130" s="17"/>
     </row>
     <row r="131" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I131" s="9"/>
+      <c r="A131" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C131" s="2">
+        <v>12.21</v>
+      </c>
+      <c r="D131" s="2">
+        <v>13008114373</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F131" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="G131" s="2">
+        <v>190</v>
+      </c>
+      <c r="H131" s="2">
+        <v>800</v>
+      </c>
+      <c r="I131" s="9">
+        <v>990</v>
+      </c>
+      <c r="J131" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K131" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L131" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M131" s="43"/>
       <c r="N131" s="17"/>
     </row>
     <row r="132" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
@@ -8468,6 +8514,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A128:O128"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="A98:O98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="A123:O123"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="G67:H67"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="L2:O2"/>
@@ -8484,25 +8549,6 @@
     <mergeCell ref="K87:L87"/>
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="A49:O49"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A68:O68"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="A128:O128"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="A98:O98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="A123:O123"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="K122:L122"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业绩表/业绩表.xlsx
+++ b/业绩表/业绩表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github本地\github\业绩表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CC487F-66A2-46C7-9F9B-A8368762A997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8556D0D1-154C-4509-A64A-77AB06D742CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8940" yWindow="930" windowWidth="19095" windowHeight="12030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="860" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="428">
   <si>
     <t>姓名</t>
   </si>
@@ -1638,6 +1638,18 @@
   </si>
   <si>
     <t>吴</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF5104888849130</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF5121195499480</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙血树叶*11</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1970,7 +1982,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2109,6 +2121,27 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2130,25 +2163,7 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2703,48 +2718,48 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="46" t="s">
+      <c r="A2" s="53" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="48" t="s">
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="54"/>
+      <c r="F2" s="55" t="s">
         <v>369</v>
       </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="50" t="s">
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="56"/>
+      <c r="K2" s="56"/>
+      <c r="L2" s="57" t="s">
         <v>370</v>
       </c>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="52"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="59"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
     <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="53">
+      <c r="A3" s="46">
         <v>45748</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-      <c r="D3" s="54"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="54"/>
-      <c r="G3" s="54"/>
-      <c r="H3" s="54"/>
-      <c r="I3" s="54"/>
-      <c r="J3" s="54"/>
-      <c r="K3" s="54"/>
-      <c r="L3" s="54"/>
-      <c r="M3" s="54"/>
-      <c r="N3" s="54"/>
-      <c r="O3" s="55"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="48"/>
     </row>
     <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -2838,23 +2853,23 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="53">
+      <c r="A6" s="46">
         <v>45778</v>
       </c>
-      <c r="B6" s="54"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54"/>
-      <c r="G6" s="54"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="54"/>
-      <c r="M6" s="54"/>
-      <c r="N6" s="54"/>
-      <c r="O6" s="55"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="48"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="22"/>
     </row>
@@ -3186,19 +3201,19 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="56" t="s">
+      <c r="G14" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="57"/>
+      <c r="H14" s="50"/>
       <c r="I14" s="6">
         <f>SUM(I7:I13)</f>
         <v>32768</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="58" t="s">
+      <c r="K14" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="59"/>
+      <c r="L14" s="52"/>
       <c r="M14" s="7">
         <f>SUM(N7:N13)</f>
         <v>6500</v>
@@ -3214,23 +3229,23 @@
       <c r="Q14" s="22"/>
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="53">
+      <c r="A15" s="46">
         <v>45809</v>
       </c>
-      <c r="B15" s="54"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="54"/>
-      <c r="J15" s="54"/>
-      <c r="K15" s="54"/>
-      <c r="L15" s="54"/>
-      <c r="M15" s="54"/>
-      <c r="N15" s="54"/>
-      <c r="O15" s="55"/>
+      <c r="B15" s="47"/>
+      <c r="C15" s="47"/>
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+      <c r="M15" s="47"/>
+      <c r="N15" s="47"/>
+      <c r="O15" s="48"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="22"/>
     </row>
@@ -3683,19 +3698,19 @@
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="56" t="s">
+      <c r="G26" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="57"/>
+      <c r="H26" s="50"/>
       <c r="I26" s="6">
         <f>SUM(I16:I25)</f>
         <v>47760</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="58" t="s">
+      <c r="K26" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="59"/>
+      <c r="L26" s="52"/>
       <c r="M26" s="7">
         <f>SUM(N18:N25)</f>
         <v>0</v>
@@ -3709,23 +3724,23 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="53">
+      <c r="A27" s="46">
         <v>45839</v>
       </c>
-      <c r="B27" s="54"/>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="55"/>
+      <c r="B27" s="47"/>
+      <c r="C27" s="47"/>
+      <c r="D27" s="47"/>
+      <c r="E27" s="47"/>
+      <c r="F27" s="47"/>
+      <c r="G27" s="47"/>
+      <c r="H27" s="47"/>
+      <c r="I27" s="47"/>
+      <c r="J27" s="47"/>
+      <c r="K27" s="47"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
+      <c r="N27" s="47"/>
+      <c r="O27" s="48"/>
     </row>
     <row r="28" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
@@ -4355,19 +4370,19 @@
         <f>G33+G35+G37+G40</f>
         <v>0</v>
       </c>
-      <c r="G42" s="56" t="s">
+      <c r="G42" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="57"/>
+      <c r="H42" s="50"/>
       <c r="I42" s="6">
         <f>SUM(I28:I41)</f>
         <v>52960</v>
       </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="58" t="s">
+      <c r="K42" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="59"/>
+      <c r="L42" s="52"/>
       <c r="M42" s="7">
         <f>SUM(N28:N41)</f>
         <v>18470</v>
@@ -4381,23 +4396,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="53">
+      <c r="A43" s="46">
         <v>45870</v>
       </c>
-      <c r="B43" s="54"/>
-      <c r="C43" s="54"/>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="54"/>
-      <c r="J43" s="54"/>
-      <c r="K43" s="54"/>
-      <c r="L43" s="54"/>
-      <c r="M43" s="54"/>
-      <c r="N43" s="54"/>
-      <c r="O43" s="55"/>
+      <c r="B43" s="47"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="47"/>
+      <c r="F43" s="47"/>
+      <c r="G43" s="47"/>
+      <c r="H43" s="47"/>
+      <c r="I43" s="47"/>
+      <c r="J43" s="47"/>
+      <c r="K43" s="47"/>
+      <c r="L43" s="47"/>
+      <c r="M43" s="47"/>
+      <c r="N43" s="47"/>
+      <c r="O43" s="48"/>
     </row>
     <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="36" t="s">
@@ -4585,19 +4600,19 @@
         <f>G46+G47</f>
         <v>585</v>
       </c>
-      <c r="G48" s="56" t="s">
+      <c r="G48" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="57"/>
+      <c r="H48" s="50"/>
       <c r="I48" s="6">
         <f>SUM(I44:I47)</f>
         <v>11470</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="58" t="s">
+      <c r="K48" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L48" s="59"/>
+      <c r="L48" s="52"/>
       <c r="M48" s="7">
         <f>SUM(N44:N47)</f>
         <v>2985</v>
@@ -4611,23 +4626,23 @@
       </c>
     </row>
     <row r="49" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="53">
+      <c r="A49" s="46">
         <v>45901</v>
       </c>
-      <c r="B49" s="54"/>
-      <c r="C49" s="54"/>
-      <c r="D49" s="54"/>
-      <c r="E49" s="54"/>
-      <c r="F49" s="54"/>
-      <c r="G49" s="54"/>
-      <c r="H49" s="54"/>
-      <c r="I49" s="54"/>
-      <c r="J49" s="54"/>
-      <c r="K49" s="54"/>
-      <c r="L49" s="54"/>
-      <c r="M49" s="54"/>
-      <c r="N49" s="54"/>
-      <c r="O49" s="55"/>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="47"/>
+      <c r="F49" s="47"/>
+      <c r="G49" s="47"/>
+      <c r="H49" s="47"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="47"/>
+      <c r="K49" s="47"/>
+      <c r="L49" s="47"/>
+      <c r="M49" s="47"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="48"/>
     </row>
     <row r="50" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
@@ -5000,19 +5015,19 @@
         <f>SUM(G51:G57)</f>
         <v>438</v>
       </c>
-      <c r="G58" s="56" t="s">
+      <c r="G58" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="57"/>
+      <c r="H58" s="50"/>
       <c r="I58" s="6">
         <f>SUM(I50:I57)</f>
         <v>35689</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="58" t="s">
+      <c r="K58" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L58" s="59"/>
+      <c r="L58" s="52"/>
       <c r="M58" s="7">
         <f>SUM(N50:N57)</f>
         <v>4186</v>
@@ -5026,23 +5041,23 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="53">
+      <c r="A59" s="46">
         <v>45931</v>
       </c>
-      <c r="B59" s="54"/>
-      <c r="C59" s="54"/>
-      <c r="D59" s="54"/>
-      <c r="E59" s="54"/>
-      <c r="F59" s="54"/>
-      <c r="G59" s="54"/>
-      <c r="H59" s="54"/>
-      <c r="I59" s="54"/>
-      <c r="J59" s="54"/>
-      <c r="K59" s="54"/>
-      <c r="L59" s="54"/>
-      <c r="M59" s="54"/>
-      <c r="N59" s="54"/>
-      <c r="O59" s="55"/>
+      <c r="B59" s="47"/>
+      <c r="C59" s="47"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="47"/>
+      <c r="F59" s="47"/>
+      <c r="G59" s="47"/>
+      <c r="H59" s="47"/>
+      <c r="I59" s="47"/>
+      <c r="J59" s="47"/>
+      <c r="K59" s="47"/>
+      <c r="L59" s="47"/>
+      <c r="M59" s="47"/>
+      <c r="N59" s="47"/>
+      <c r="O59" s="48"/>
     </row>
     <row r="60" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
@@ -5365,19 +5380,19 @@
         <f>SUM(G60:G66)</f>
         <v>640</v>
       </c>
-      <c r="G67" s="56" t="s">
+      <c r="G67" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="57"/>
+      <c r="H67" s="50"/>
       <c r="I67" s="6">
         <f>SUM(I60:I66)</f>
         <v>26988</v>
       </c>
       <c r="J67" s="5"/>
-      <c r="K67" s="58" t="s">
+      <c r="K67" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L67" s="59"/>
+      <c r="L67" s="52"/>
       <c r="M67" s="7">
         <f>SUM(N57:N66)</f>
         <v>0</v>
@@ -5391,23 +5406,23 @@
       </c>
     </row>
     <row r="68" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="53">
+      <c r="A68" s="46">
         <v>45962</v>
       </c>
-      <c r="B68" s="54"/>
-      <c r="C68" s="54"/>
-      <c r="D68" s="54"/>
-      <c r="E68" s="54"/>
-      <c r="F68" s="54"/>
-      <c r="G68" s="54"/>
-      <c r="H68" s="54"/>
-      <c r="I68" s="54"/>
-      <c r="J68" s="54"/>
-      <c r="K68" s="54"/>
-      <c r="L68" s="54"/>
-      <c r="M68" s="54"/>
-      <c r="N68" s="54"/>
-      <c r="O68" s="55"/>
+      <c r="B68" s="47"/>
+      <c r="C68" s="47"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="47"/>
+      <c r="F68" s="47"/>
+      <c r="G68" s="47"/>
+      <c r="H68" s="47"/>
+      <c r="I68" s="47"/>
+      <c r="J68" s="47"/>
+      <c r="K68" s="47"/>
+      <c r="L68" s="47"/>
+      <c r="M68" s="47"/>
+      <c r="N68" s="47"/>
+      <c r="O68" s="48"/>
     </row>
     <row r="69" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
@@ -6223,19 +6238,19 @@
         <f>SUM(G69:G80)</f>
         <v>3062</v>
       </c>
-      <c r="G87" s="56" t="s">
+      <c r="G87" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H87" s="57"/>
+      <c r="H87" s="50"/>
       <c r="I87" s="6">
         <f>SUM(I69:I86)</f>
         <v>123444</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="58" t="s">
+      <c r="K87" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L87" s="59"/>
+      <c r="L87" s="52"/>
       <c r="M87" s="7">
         <f>SUM(N69:N85)</f>
         <v>87602</v>
@@ -6249,23 +6264,23 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="53">
+      <c r="A88" s="46">
         <v>45992</v>
       </c>
-      <c r="B88" s="54"/>
-      <c r="C88" s="54"/>
-      <c r="D88" s="54"/>
-      <c r="E88" s="54"/>
-      <c r="F88" s="54"/>
-      <c r="G88" s="54"/>
-      <c r="H88" s="54"/>
-      <c r="I88" s="54"/>
-      <c r="J88" s="54"/>
-      <c r="K88" s="54"/>
-      <c r="L88" s="54"/>
-      <c r="M88" s="54"/>
-      <c r="N88" s="54"/>
-      <c r="O88" s="55"/>
+      <c r="B88" s="47"/>
+      <c r="C88" s="47"/>
+      <c r="D88" s="47"/>
+      <c r="E88" s="47"/>
+      <c r="F88" s="47"/>
+      <c r="G88" s="47"/>
+      <c r="H88" s="47"/>
+      <c r="I88" s="47"/>
+      <c r="J88" s="47"/>
+      <c r="K88" s="47"/>
+      <c r="L88" s="47"/>
+      <c r="M88" s="47"/>
+      <c r="N88" s="47"/>
+      <c r="O88" s="48"/>
     </row>
     <row r="89" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
@@ -6628,19 +6643,19 @@
         <f>SUM(G76:G87)</f>
         <v>4470</v>
       </c>
-      <c r="G97" s="56" t="s">
+      <c r="G97" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="57"/>
+      <c r="H97" s="50"/>
       <c r="I97" s="6">
         <f>SUM(I89:I96)</f>
         <v>27632</v>
       </c>
       <c r="J97" s="5"/>
-      <c r="K97" s="58" t="s">
+      <c r="K97" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L97" s="59"/>
+      <c r="L97" s="52"/>
       <c r="M97" s="7">
         <f>SUM(N89:N94)</f>
         <v>0</v>
@@ -6654,23 +6669,23 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="53">
+      <c r="A98" s="46">
         <v>46023</v>
       </c>
-      <c r="B98" s="54"/>
-      <c r="C98" s="54"/>
-      <c r="D98" s="54"/>
-      <c r="E98" s="54"/>
-      <c r="F98" s="54"/>
-      <c r="G98" s="54"/>
-      <c r="H98" s="54"/>
-      <c r="I98" s="54"/>
-      <c r="J98" s="54"/>
-      <c r="K98" s="54"/>
-      <c r="L98" s="54"/>
-      <c r="M98" s="54"/>
-      <c r="N98" s="54"/>
-      <c r="O98" s="55"/>
+      <c r="B98" s="47"/>
+      <c r="C98" s="47"/>
+      <c r="D98" s="47"/>
+      <c r="E98" s="47"/>
+      <c r="F98" s="47"/>
+      <c r="G98" s="47"/>
+      <c r="H98" s="47"/>
+      <c r="I98" s="47"/>
+      <c r="J98" s="47"/>
+      <c r="K98" s="47"/>
+      <c r="L98" s="47"/>
+      <c r="M98" s="47"/>
+      <c r="N98" s="47"/>
+      <c r="O98" s="48"/>
     </row>
     <row r="99" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="38" t="s">
@@ -7694,19 +7709,19 @@
         <f>SUM(G106:G117)</f>
         <v>2483</v>
       </c>
-      <c r="G122" s="56" t="s">
+      <c r="G122" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H122" s="57"/>
+      <c r="H122" s="50"/>
       <c r="I122" s="6">
         <f>SUM(I99:I121)</f>
         <v>53972</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="58" t="s">
+      <c r="K122" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L122" s="59"/>
+      <c r="L122" s="52"/>
       <c r="M122" s="7">
         <f>SUM(N99:N121)</f>
         <v>30730</v>
@@ -7720,23 +7735,23 @@
       </c>
     </row>
     <row r="123" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="53">
+      <c r="A123" s="46">
         <v>46054</v>
       </c>
-      <c r="B123" s="54"/>
-      <c r="C123" s="54"/>
-      <c r="D123" s="54"/>
-      <c r="E123" s="54"/>
-      <c r="F123" s="54"/>
-      <c r="G123" s="54"/>
-      <c r="H123" s="54"/>
-      <c r="I123" s="54"/>
-      <c r="J123" s="54"/>
-      <c r="K123" s="54"/>
-      <c r="L123" s="54"/>
-      <c r="M123" s="54"/>
-      <c r="N123" s="54"/>
-      <c r="O123" s="55"/>
+      <c r="B123" s="47"/>
+      <c r="C123" s="47"/>
+      <c r="D123" s="47"/>
+      <c r="E123" s="47"/>
+      <c r="F123" s="47"/>
+      <c r="G123" s="47"/>
+      <c r="H123" s="47"/>
+      <c r="I123" s="47"/>
+      <c r="J123" s="47"/>
+      <c r="K123" s="47"/>
+      <c r="L123" s="47"/>
+      <c r="M123" s="47"/>
+      <c r="N123" s="47"/>
+      <c r="O123" s="48"/>
     </row>
     <row r="124" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
@@ -7876,19 +7891,19 @@
         <f>SUM(G110:G121)</f>
         <v>2121</v>
       </c>
-      <c r="G127" s="56" t="s">
+      <c r="G127" s="49" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="57"/>
+      <c r="H127" s="50"/>
       <c r="I127" s="6">
         <f>SUM(I124:I126)</f>
         <v>6587</v>
       </c>
       <c r="J127" s="5"/>
-      <c r="K127" s="58" t="s">
+      <c r="K127" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="59"/>
+      <c r="L127" s="52"/>
       <c r="M127" s="7">
         <f>SUM(N124:N125)</f>
         <v>0</v>
@@ -7902,25 +7917,25 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="53">
+      <c r="A128" s="46">
         <v>46082</v>
       </c>
-      <c r="B128" s="54"/>
-      <c r="C128" s="54"/>
-      <c r="D128" s="54"/>
-      <c r="E128" s="54"/>
-      <c r="F128" s="54"/>
-      <c r="G128" s="54"/>
-      <c r="H128" s="54"/>
-      <c r="I128" s="54"/>
-      <c r="J128" s="54"/>
-      <c r="K128" s="54"/>
-      <c r="L128" s="54"/>
-      <c r="M128" s="54"/>
-      <c r="N128" s="54"/>
-      <c r="O128" s="55"/>
-    </row>
-    <row r="129" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B128" s="47"/>
+      <c r="C128" s="47"/>
+      <c r="D128" s="47"/>
+      <c r="E128" s="47"/>
+      <c r="F128" s="47"/>
+      <c r="G128" s="47"/>
+      <c r="H128" s="47"/>
+      <c r="I128" s="47"/>
+      <c r="J128" s="47"/>
+      <c r="K128" s="47"/>
+      <c r="L128" s="47"/>
+      <c r="M128" s="47"/>
+      <c r="N128" s="47"/>
+      <c r="O128" s="48"/>
+    </row>
+    <row r="129" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
         <v>417</v>
       </c>
@@ -7962,7 +7977,7 @@
       </c>
       <c r="N129" s="17"/>
     </row>
-    <row r="130" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
         <v>361</v>
       </c>
@@ -8004,7 +8019,7 @@
       </c>
       <c r="N130" s="17"/>
     </row>
-    <row r="131" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>376</v>
       </c>
@@ -8041,58 +8056,99 @@
       <c r="L131" s="2">
         <v>3.6</v>
       </c>
-      <c r="M131" s="43"/>
+      <c r="M131" s="60" t="s">
+        <v>425</v>
+      </c>
       <c r="N131" s="17"/>
     </row>
-    <row r="132" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I132" s="9"/>
+    <row r="132" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A132" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C132" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="D132" s="2">
+        <v>13624833466</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="G132" s="2">
+        <v>100</v>
+      </c>
+      <c r="H132" s="2">
+        <v>900</v>
+      </c>
+      <c r="I132" s="9">
+        <v>1000</v>
+      </c>
+      <c r="J132" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K132" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L132" s="2">
+        <v>3.6</v>
+      </c>
+      <c r="M132" s="60" t="s">
+        <v>426</v>
+      </c>
       <c r="N132" s="17"/>
-    </row>
-    <row r="133" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O132" s="1"/>
+    </row>
+    <row r="133" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I133" s="9"/>
       <c r="N133" s="17"/>
     </row>
-    <row r="134" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I134" s="9"/>
       <c r="N134" s="17"/>
     </row>
-    <row r="135" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I135" s="9"/>
       <c r="N135" s="17"/>
     </row>
-    <row r="136" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I136" s="9"/>
       <c r="N136" s="17"/>
     </row>
-    <row r="137" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I137" s="9"/>
       <c r="N137" s="17"/>
     </row>
-    <row r="138" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I138" s="9"/>
       <c r="N138" s="17"/>
     </row>
-    <row r="139" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I139" s="9"/>
       <c r="N139" s="17"/>
     </row>
-    <row r="140" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I140" s="9"/>
       <c r="N140" s="17"/>
     </row>
-    <row r="141" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I141" s="9"/>
       <c r="N141" s="17"/>
     </row>
-    <row r="142" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I142" s="9"/>
       <c r="N142" s="17"/>
     </row>
-    <row r="143" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I143" s="9"/>
       <c r="N143" s="17"/>
     </row>
-    <row r="144" spans="1:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I144" s="9"/>
       <c r="N144" s="17"/>
     </row>
@@ -8514,25 +8570,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A128:O128"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="A98:O98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="A123:O123"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A68:O68"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="G67:H67"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="L2:O2"/>
@@ -8549,6 +8586,25 @@
     <mergeCell ref="K87:L87"/>
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="A128:O128"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="A98:O98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="A123:O123"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="K122:L122"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业绩表/业绩表.xlsx
+++ b/业绩表/业绩表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github本地\github\业绩表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8556D0D1-154C-4509-A64A-77AB06D742CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F982149A-9A4B-437C-A528-35687F2BEB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="432">
   <si>
     <t>姓名</t>
   </si>
@@ -1650,6 +1650,21 @@
   </si>
   <si>
     <t>龙血树叶*11</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 沈元龙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>元龙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>广西壮族自治区柳州市鱼峰区古亭大道268号</t>
+  </si>
+  <si>
+    <t>冬虫夏草胶丸*4+补肾安神口服液*2+药王石水杯*1+药王石能量吊坠*1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2121,25 +2136,7 @@
     <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2163,7 +2160,25 @@
     <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2718,48 +2733,48 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="53" t="s">
+      <c r="A2" s="47" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="55" t="s">
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="49" t="s">
         <v>369</v>
       </c>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
-      <c r="K2" s="56"/>
-      <c r="L2" s="57" t="s">
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="51" t="s">
         <v>370</v>
       </c>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="59"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="53"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
     <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="46">
+      <c r="A3" s="54">
         <v>45748</v>
       </c>
-      <c r="B3" s="47"/>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="48"/>
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
+      <c r="K3" s="55"/>
+      <c r="L3" s="55"/>
+      <c r="M3" s="55"/>
+      <c r="N3" s="55"/>
+      <c r="O3" s="56"/>
     </row>
     <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -2853,23 +2868,23 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="46">
+      <c r="A6" s="54">
         <v>45778</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="47"/>
-      <c r="I6" s="47"/>
-      <c r="J6" s="47"/>
-      <c r="K6" s="47"/>
-      <c r="L6" s="47"/>
-      <c r="M6" s="47"/>
-      <c r="N6" s="47"/>
-      <c r="O6" s="48"/>
+      <c r="B6" s="55"/>
+      <c r="C6" s="55"/>
+      <c r="D6" s="55"/>
+      <c r="E6" s="55"/>
+      <c r="F6" s="55"/>
+      <c r="G6" s="55"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="55"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="55"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="55"/>
+      <c r="N6" s="55"/>
+      <c r="O6" s="56"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="22"/>
     </row>
@@ -3201,19 +3216,19 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="49" t="s">
+      <c r="G14" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="50"/>
+      <c r="H14" s="58"/>
       <c r="I14" s="6">
         <f>SUM(I7:I13)</f>
         <v>32768</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="51" t="s">
+      <c r="K14" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="52"/>
+      <c r="L14" s="60"/>
       <c r="M14" s="7">
         <f>SUM(N7:N13)</f>
         <v>6500</v>
@@ -3229,23 +3244,23 @@
       <c r="Q14" s="22"/>
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="46">
+      <c r="A15" s="54">
         <v>45809</v>
       </c>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="47"/>
-      <c r="I15" s="47"/>
-      <c r="J15" s="47"/>
-      <c r="K15" s="47"/>
-      <c r="L15" s="47"/>
-      <c r="M15" s="47"/>
-      <c r="N15" s="47"/>
-      <c r="O15" s="48"/>
+      <c r="B15" s="55"/>
+      <c r="C15" s="55"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="55"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="55"/>
+      <c r="H15" s="55"/>
+      <c r="I15" s="55"/>
+      <c r="J15" s="55"/>
+      <c r="K15" s="55"/>
+      <c r="L15" s="55"/>
+      <c r="M15" s="55"/>
+      <c r="N15" s="55"/>
+      <c r="O15" s="56"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="22"/>
     </row>
@@ -3698,19 +3713,19 @@
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="49" t="s">
+      <c r="G26" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="50"/>
+      <c r="H26" s="58"/>
       <c r="I26" s="6">
         <f>SUM(I16:I25)</f>
         <v>47760</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="51" t="s">
+      <c r="K26" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="52"/>
+      <c r="L26" s="60"/>
       <c r="M26" s="7">
         <f>SUM(N18:N25)</f>
         <v>0</v>
@@ -3724,23 +3739,23 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="46">
+      <c r="A27" s="54">
         <v>45839</v>
       </c>
-      <c r="B27" s="47"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="47"/>
-      <c r="E27" s="47"/>
-      <c r="F27" s="47"/>
-      <c r="G27" s="47"/>
-      <c r="H27" s="47"/>
-      <c r="I27" s="47"/>
-      <c r="J27" s="47"/>
-      <c r="K27" s="47"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
-      <c r="N27" s="47"/>
-      <c r="O27" s="48"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="55"/>
+      <c r="F27" s="55"/>
+      <c r="G27" s="55"/>
+      <c r="H27" s="55"/>
+      <c r="I27" s="55"/>
+      <c r="J27" s="55"/>
+      <c r="K27" s="55"/>
+      <c r="L27" s="55"/>
+      <c r="M27" s="55"/>
+      <c r="N27" s="55"/>
+      <c r="O27" s="56"/>
     </row>
     <row r="28" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
@@ -4370,19 +4385,19 @@
         <f>G33+G35+G37+G40</f>
         <v>0</v>
       </c>
-      <c r="G42" s="49" t="s">
+      <c r="G42" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="50"/>
+      <c r="H42" s="58"/>
       <c r="I42" s="6">
         <f>SUM(I28:I41)</f>
         <v>52960</v>
       </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="51" t="s">
+      <c r="K42" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="52"/>
+      <c r="L42" s="60"/>
       <c r="M42" s="7">
         <f>SUM(N28:N41)</f>
         <v>18470</v>
@@ -4396,23 +4411,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="46">
+      <c r="A43" s="54">
         <v>45870</v>
       </c>
-      <c r="B43" s="47"/>
-      <c r="C43" s="47"/>
-      <c r="D43" s="47"/>
-      <c r="E43" s="47"/>
-      <c r="F43" s="47"/>
-      <c r="G43" s="47"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="47"/>
-      <c r="J43" s="47"/>
-      <c r="K43" s="47"/>
-      <c r="L43" s="47"/>
-      <c r="M43" s="47"/>
-      <c r="N43" s="47"/>
-      <c r="O43" s="48"/>
+      <c r="B43" s="55"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="55"/>
+      <c r="F43" s="55"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="55"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="55"/>
+      <c r="M43" s="55"/>
+      <c r="N43" s="55"/>
+      <c r="O43" s="56"/>
     </row>
     <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="36" t="s">
@@ -4600,19 +4615,19 @@
         <f>G46+G47</f>
         <v>585</v>
       </c>
-      <c r="G48" s="49" t="s">
+      <c r="G48" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="50"/>
+      <c r="H48" s="58"/>
       <c r="I48" s="6">
         <f>SUM(I44:I47)</f>
         <v>11470</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="51" t="s">
+      <c r="K48" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L48" s="52"/>
+      <c r="L48" s="60"/>
       <c r="M48" s="7">
         <f>SUM(N44:N47)</f>
         <v>2985</v>
@@ -4626,23 +4641,23 @@
       </c>
     </row>
     <row r="49" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="46">
+      <c r="A49" s="54">
         <v>45901</v>
       </c>
-      <c r="B49" s="47"/>
-      <c r="C49" s="47"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="47"/>
-      <c r="F49" s="47"/>
-      <c r="G49" s="47"/>
-      <c r="H49" s="47"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="47"/>
-      <c r="K49" s="47"/>
-      <c r="L49" s="47"/>
-      <c r="M49" s="47"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="48"/>
+      <c r="B49" s="55"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="55"/>
+      <c r="E49" s="55"/>
+      <c r="F49" s="55"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="55"/>
+      <c r="K49" s="55"/>
+      <c r="L49" s="55"/>
+      <c r="M49" s="55"/>
+      <c r="N49" s="55"/>
+      <c r="O49" s="56"/>
     </row>
     <row r="50" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
@@ -5015,19 +5030,19 @@
         <f>SUM(G51:G57)</f>
         <v>438</v>
       </c>
-      <c r="G58" s="49" t="s">
+      <c r="G58" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="50"/>
+      <c r="H58" s="58"/>
       <c r="I58" s="6">
         <f>SUM(I50:I57)</f>
         <v>35689</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="51" t="s">
+      <c r="K58" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L58" s="52"/>
+      <c r="L58" s="60"/>
       <c r="M58" s="7">
         <f>SUM(N50:N57)</f>
         <v>4186</v>
@@ -5041,23 +5056,23 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="46">
+      <c r="A59" s="54">
         <v>45931</v>
       </c>
-      <c r="B59" s="47"/>
-      <c r="C59" s="47"/>
-      <c r="D59" s="47"/>
-      <c r="E59" s="47"/>
-      <c r="F59" s="47"/>
-      <c r="G59" s="47"/>
-      <c r="H59" s="47"/>
-      <c r="I59" s="47"/>
-      <c r="J59" s="47"/>
-      <c r="K59" s="47"/>
-      <c r="L59" s="47"/>
-      <c r="M59" s="47"/>
-      <c r="N59" s="47"/>
-      <c r="O59" s="48"/>
+      <c r="B59" s="55"/>
+      <c r="C59" s="55"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="55"/>
+      <c r="F59" s="55"/>
+      <c r="G59" s="55"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="55"/>
+      <c r="J59" s="55"/>
+      <c r="K59" s="55"/>
+      <c r="L59" s="55"/>
+      <c r="M59" s="55"/>
+      <c r="N59" s="55"/>
+      <c r="O59" s="56"/>
     </row>
     <row r="60" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
@@ -5380,19 +5395,19 @@
         <f>SUM(G60:G66)</f>
         <v>640</v>
       </c>
-      <c r="G67" s="49" t="s">
+      <c r="G67" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="50"/>
+      <c r="H67" s="58"/>
       <c r="I67" s="6">
         <f>SUM(I60:I66)</f>
         <v>26988</v>
       </c>
       <c r="J67" s="5"/>
-      <c r="K67" s="51" t="s">
+      <c r="K67" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L67" s="52"/>
+      <c r="L67" s="60"/>
       <c r="M67" s="7">
         <f>SUM(N57:N66)</f>
         <v>0</v>
@@ -5406,23 +5421,23 @@
       </c>
     </row>
     <row r="68" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="46">
+      <c r="A68" s="54">
         <v>45962</v>
       </c>
-      <c r="B68" s="47"/>
-      <c r="C68" s="47"/>
-      <c r="D68" s="47"/>
-      <c r="E68" s="47"/>
-      <c r="F68" s="47"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="47"/>
-      <c r="I68" s="47"/>
-      <c r="J68" s="47"/>
-      <c r="K68" s="47"/>
-      <c r="L68" s="47"/>
-      <c r="M68" s="47"/>
-      <c r="N68" s="47"/>
-      <c r="O68" s="48"/>
+      <c r="B68" s="55"/>
+      <c r="C68" s="55"/>
+      <c r="D68" s="55"/>
+      <c r="E68" s="55"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="55"/>
+      <c r="H68" s="55"/>
+      <c r="I68" s="55"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="55"/>
+      <c r="L68" s="55"/>
+      <c r="M68" s="55"/>
+      <c r="N68" s="55"/>
+      <c r="O68" s="56"/>
     </row>
     <row r="69" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
@@ -6238,19 +6253,19 @@
         <f>SUM(G69:G80)</f>
         <v>3062</v>
       </c>
-      <c r="G87" s="49" t="s">
+      <c r="G87" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H87" s="50"/>
+      <c r="H87" s="58"/>
       <c r="I87" s="6">
         <f>SUM(I69:I86)</f>
         <v>123444</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="51" t="s">
+      <c r="K87" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L87" s="52"/>
+      <c r="L87" s="60"/>
       <c r="M87" s="7">
         <f>SUM(N69:N85)</f>
         <v>87602</v>
@@ -6264,23 +6279,23 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="46">
+      <c r="A88" s="54">
         <v>45992</v>
       </c>
-      <c r="B88" s="47"/>
-      <c r="C88" s="47"/>
-      <c r="D88" s="47"/>
-      <c r="E88" s="47"/>
-      <c r="F88" s="47"/>
-      <c r="G88" s="47"/>
-      <c r="H88" s="47"/>
-      <c r="I88" s="47"/>
-      <c r="J88" s="47"/>
-      <c r="K88" s="47"/>
-      <c r="L88" s="47"/>
-      <c r="M88" s="47"/>
-      <c r="N88" s="47"/>
-      <c r="O88" s="48"/>
+      <c r="B88" s="55"/>
+      <c r="C88" s="55"/>
+      <c r="D88" s="55"/>
+      <c r="E88" s="55"/>
+      <c r="F88" s="55"/>
+      <c r="G88" s="55"/>
+      <c r="H88" s="55"/>
+      <c r="I88" s="55"/>
+      <c r="J88" s="55"/>
+      <c r="K88" s="55"/>
+      <c r="L88" s="55"/>
+      <c r="M88" s="55"/>
+      <c r="N88" s="55"/>
+      <c r="O88" s="56"/>
     </row>
     <row r="89" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
@@ -6643,19 +6658,19 @@
         <f>SUM(G76:G87)</f>
         <v>4470</v>
       </c>
-      <c r="G97" s="49" t="s">
+      <c r="G97" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="50"/>
+      <c r="H97" s="58"/>
       <c r="I97" s="6">
         <f>SUM(I89:I96)</f>
         <v>27632</v>
       </c>
       <c r="J97" s="5"/>
-      <c r="K97" s="51" t="s">
+      <c r="K97" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L97" s="52"/>
+      <c r="L97" s="60"/>
       <c r="M97" s="7">
         <f>SUM(N89:N94)</f>
         <v>0</v>
@@ -6669,23 +6684,23 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="46">
+      <c r="A98" s="54">
         <v>46023</v>
       </c>
-      <c r="B98" s="47"/>
-      <c r="C98" s="47"/>
-      <c r="D98" s="47"/>
-      <c r="E98" s="47"/>
-      <c r="F98" s="47"/>
-      <c r="G98" s="47"/>
-      <c r="H98" s="47"/>
-      <c r="I98" s="47"/>
-      <c r="J98" s="47"/>
-      <c r="K98" s="47"/>
-      <c r="L98" s="47"/>
-      <c r="M98" s="47"/>
-      <c r="N98" s="47"/>
-      <c r="O98" s="48"/>
+      <c r="B98" s="55"/>
+      <c r="C98" s="55"/>
+      <c r="D98" s="55"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="55"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="55"/>
+      <c r="K98" s="55"/>
+      <c r="L98" s="55"/>
+      <c r="M98" s="55"/>
+      <c r="N98" s="55"/>
+      <c r="O98" s="56"/>
     </row>
     <row r="99" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="38" t="s">
@@ -7709,19 +7724,19 @@
         <f>SUM(G106:G117)</f>
         <v>2483</v>
       </c>
-      <c r="G122" s="49" t="s">
+      <c r="G122" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H122" s="50"/>
+      <c r="H122" s="58"/>
       <c r="I122" s="6">
         <f>SUM(I99:I121)</f>
         <v>53972</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="51" t="s">
+      <c r="K122" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L122" s="52"/>
+      <c r="L122" s="60"/>
       <c r="M122" s="7">
         <f>SUM(N99:N121)</f>
         <v>30730</v>
@@ -7735,23 +7750,23 @@
       </c>
     </row>
     <row r="123" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="46">
+      <c r="A123" s="54">
         <v>46054</v>
       </c>
-      <c r="B123" s="47"/>
-      <c r="C123" s="47"/>
-      <c r="D123" s="47"/>
-      <c r="E123" s="47"/>
-      <c r="F123" s="47"/>
-      <c r="G123" s="47"/>
-      <c r="H123" s="47"/>
-      <c r="I123" s="47"/>
-      <c r="J123" s="47"/>
-      <c r="K123" s="47"/>
-      <c r="L123" s="47"/>
-      <c r="M123" s="47"/>
-      <c r="N123" s="47"/>
-      <c r="O123" s="48"/>
+      <c r="B123" s="55"/>
+      <c r="C123" s="55"/>
+      <c r="D123" s="55"/>
+      <c r="E123" s="55"/>
+      <c r="F123" s="55"/>
+      <c r="G123" s="55"/>
+      <c r="H123" s="55"/>
+      <c r="I123" s="55"/>
+      <c r="J123" s="55"/>
+      <c r="K123" s="55"/>
+      <c r="L123" s="55"/>
+      <c r="M123" s="55"/>
+      <c r="N123" s="55"/>
+      <c r="O123" s="56"/>
     </row>
     <row r="124" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
@@ -7891,19 +7906,19 @@
         <f>SUM(G110:G121)</f>
         <v>2121</v>
       </c>
-      <c r="G127" s="49" t="s">
+      <c r="G127" s="57" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="50"/>
+      <c r="H127" s="58"/>
       <c r="I127" s="6">
         <f>SUM(I124:I126)</f>
         <v>6587</v>
       </c>
       <c r="J127" s="5"/>
-      <c r="K127" s="51" t="s">
+      <c r="K127" s="59" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="52"/>
+      <c r="L127" s="60"/>
       <c r="M127" s="7">
         <f>SUM(N124:N125)</f>
         <v>0</v>
@@ -7917,23 +7932,23 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="46">
+      <c r="A128" s="54">
         <v>46082</v>
       </c>
-      <c r="B128" s="47"/>
-      <c r="C128" s="47"/>
-      <c r="D128" s="47"/>
-      <c r="E128" s="47"/>
-      <c r="F128" s="47"/>
-      <c r="G128" s="47"/>
-      <c r="H128" s="47"/>
-      <c r="I128" s="47"/>
-      <c r="J128" s="47"/>
-      <c r="K128" s="47"/>
-      <c r="L128" s="47"/>
-      <c r="M128" s="47"/>
-      <c r="N128" s="47"/>
-      <c r="O128" s="48"/>
+      <c r="B128" s="55"/>
+      <c r="C128" s="55"/>
+      <c r="D128" s="55"/>
+      <c r="E128" s="55"/>
+      <c r="F128" s="55"/>
+      <c r="G128" s="55"/>
+      <c r="H128" s="55"/>
+      <c r="I128" s="55"/>
+      <c r="J128" s="55"/>
+      <c r="K128" s="55"/>
+      <c r="L128" s="55"/>
+      <c r="M128" s="55"/>
+      <c r="N128" s="55"/>
+      <c r="O128" s="56"/>
     </row>
     <row r="129" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
@@ -7967,7 +7982,7 @@
         <v>55</v>
       </c>
       <c r="K129" s="1" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="L129" s="2">
         <v>3.5</v>
@@ -7976,6 +7991,9 @@
         <v>422</v>
       </c>
       <c r="N129" s="17"/>
+      <c r="O129" s="1" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="130" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="1" t="s">
@@ -8051,12 +8069,12 @@
         <v>59</v>
       </c>
       <c r="K131" s="1" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="L131" s="2">
         <v>3.6</v>
       </c>
-      <c r="M131" s="60" t="s">
+      <c r="M131" s="46" t="s">
         <v>425</v>
       </c>
       <c r="N131" s="17"/>
@@ -8098,14 +8116,49 @@
       <c r="L132" s="2">
         <v>3.6</v>
       </c>
-      <c r="M132" s="60" t="s">
+      <c r="M132" s="46" t="s">
         <v>426</v>
       </c>
       <c r="N132" s="17"/>
       <c r="O132" s="1"/>
     </row>
     <row r="133" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I133" s="9"/>
+      <c r="A133" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="C133" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="D133" s="2">
+        <v>15577119500</v>
+      </c>
+      <c r="E133" s="43" t="s">
+        <v>430</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G133" s="2">
+        <v>800</v>
+      </c>
+      <c r="H133" s="2">
+        <v>1060</v>
+      </c>
+      <c r="I133" s="9">
+        <v>1860</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L133" s="2">
+        <v>3.11</v>
+      </c>
       <c r="N133" s="17"/>
     </row>
     <row r="134" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
@@ -8570,6 +8623,25 @@
     </row>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="A128:O128"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="A98:O98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="A123:O123"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="K122:L122"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="G67:H67"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="L2:O2"/>
@@ -8586,25 +8658,6 @@
     <mergeCell ref="K87:L87"/>
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="A49:O49"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A68:O68"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="G67:H67"/>
-    <mergeCell ref="A128:O128"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="A98:O98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="A123:O123"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="K122:L122"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业绩表/业绩表.xlsx
+++ b/业绩表/业绩表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github本地\github\业绩表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F982149A-9A4B-437C-A528-35687F2BEB2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF98D37-21EF-4C5D-BBAE-1635E4FDD022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2520" yWindow="1695" windowWidth="19095" windowHeight="12030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="431">
   <si>
     <t>姓名</t>
   </si>
@@ -1653,18 +1653,15 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 沈元龙</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>元龙</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>广西壮族自治区柳州市鱼峰区古亭大道268号</t>
-  </si>
-  <si>
-    <t>冬虫夏草胶丸*4+补肾安神口服液*2+药王石水杯*1+药王石能量吊坠*1</t>
+    <t>吉林省延边州延吉市河南街新地小区4号楼三单元202</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参蛾温肾口服液*5 无事牌*1 五虫通脉液*1 西红花*10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>参蛾温肾口服液*10 无事牌*2 五虫通脉液*2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -2139,6 +2136,27 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2158,27 +2176,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2733,48 +2730,48 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="54" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="49" t="s">
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="56" t="s">
         <v>369</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-      <c r="L2" s="51" t="s">
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="57"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="58" t="s">
         <v>370</v>
       </c>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="53"/>
+      <c r="M2" s="59"/>
+      <c r="N2" s="59"/>
+      <c r="O2" s="60"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
     <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="54">
+      <c r="A3" s="47">
         <v>45748</v>
       </c>
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
-      <c r="I3" s="55"/>
-      <c r="J3" s="55"/>
-      <c r="K3" s="55"/>
-      <c r="L3" s="55"/>
-      <c r="M3" s="55"/>
-      <c r="N3" s="55"/>
-      <c r="O3" s="56"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="49"/>
     </row>
     <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -2868,23 +2865,23 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="54">
+      <c r="A6" s="47">
         <v>45778</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-      <c r="K6" s="55"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="55"/>
-      <c r="N6" s="55"/>
-      <c r="O6" s="56"/>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+      <c r="M6" s="48"/>
+      <c r="N6" s="48"/>
+      <c r="O6" s="49"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="22"/>
     </row>
@@ -3216,19 +3213,19 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="57" t="s">
+      <c r="G14" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="58"/>
+      <c r="H14" s="51"/>
       <c r="I14" s="6">
         <f>SUM(I7:I13)</f>
         <v>32768</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="59" t="s">
+      <c r="K14" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="60"/>
+      <c r="L14" s="53"/>
       <c r="M14" s="7">
         <f>SUM(N7:N13)</f>
         <v>6500</v>
@@ -3244,23 +3241,23 @@
       <c r="Q14" s="22"/>
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="54">
+      <c r="A15" s="47">
         <v>45809</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
-      <c r="I15" s="55"/>
-      <c r="J15" s="55"/>
-      <c r="K15" s="55"/>
-      <c r="L15" s="55"/>
-      <c r="M15" s="55"/>
-      <c r="N15" s="55"/>
-      <c r="O15" s="56"/>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="48"/>
+      <c r="K15" s="48"/>
+      <c r="L15" s="48"/>
+      <c r="M15" s="48"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="49"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="22"/>
     </row>
@@ -3713,19 +3710,19 @@
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="57" t="s">
+      <c r="G26" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="58"/>
+      <c r="H26" s="51"/>
       <c r="I26" s="6">
         <f>SUM(I16:I25)</f>
         <v>47760</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="59" t="s">
+      <c r="K26" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="60"/>
+      <c r="L26" s="53"/>
       <c r="M26" s="7">
         <f>SUM(N18:N25)</f>
         <v>0</v>
@@ -3739,23 +3736,23 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="54">
+      <c r="A27" s="47">
         <v>45839</v>
       </c>
-      <c r="B27" s="55"/>
-      <c r="C27" s="55"/>
-      <c r="D27" s="55"/>
-      <c r="E27" s="55"/>
-      <c r="F27" s="55"/>
-      <c r="G27" s="55"/>
-      <c r="H27" s="55"/>
-      <c r="I27" s="55"/>
-      <c r="J27" s="55"/>
-      <c r="K27" s="55"/>
-      <c r="L27" s="55"/>
-      <c r="M27" s="55"/>
-      <c r="N27" s="55"/>
-      <c r="O27" s="56"/>
+      <c r="B27" s="48"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="48"/>
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="48"/>
+      <c r="H27" s="48"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="48"/>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="49"/>
     </row>
     <row r="28" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
@@ -4385,19 +4382,19 @@
         <f>G33+G35+G37+G40</f>
         <v>0</v>
       </c>
-      <c r="G42" s="57" t="s">
+      <c r="G42" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="58"/>
+      <c r="H42" s="51"/>
       <c r="I42" s="6">
         <f>SUM(I28:I41)</f>
         <v>52960</v>
       </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="59" t="s">
+      <c r="K42" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="60"/>
+      <c r="L42" s="53"/>
       <c r="M42" s="7">
         <f>SUM(N28:N41)</f>
         <v>18470</v>
@@ -4411,23 +4408,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="54">
+      <c r="A43" s="47">
         <v>45870</v>
       </c>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="55"/>
-      <c r="F43" s="55"/>
-      <c r="G43" s="55"/>
-      <c r="H43" s="55"/>
-      <c r="I43" s="55"/>
-      <c r="J43" s="55"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="55"/>
-      <c r="M43" s="55"/>
-      <c r="N43" s="55"/>
-      <c r="O43" s="56"/>
+      <c r="B43" s="48"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="48"/>
+      <c r="E43" s="48"/>
+      <c r="F43" s="48"/>
+      <c r="G43" s="48"/>
+      <c r="H43" s="48"/>
+      <c r="I43" s="48"/>
+      <c r="J43" s="48"/>
+      <c r="K43" s="48"/>
+      <c r="L43" s="48"/>
+      <c r="M43" s="48"/>
+      <c r="N43" s="48"/>
+      <c r="O43" s="49"/>
     </row>
     <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="36" t="s">
@@ -4615,19 +4612,19 @@
         <f>G46+G47</f>
         <v>585</v>
       </c>
-      <c r="G48" s="57" t="s">
+      <c r="G48" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="58"/>
+      <c r="H48" s="51"/>
       <c r="I48" s="6">
         <f>SUM(I44:I47)</f>
         <v>11470</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="59" t="s">
+      <c r="K48" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L48" s="60"/>
+      <c r="L48" s="53"/>
       <c r="M48" s="7">
         <f>SUM(N44:N47)</f>
         <v>2985</v>
@@ -4641,23 +4638,23 @@
       </c>
     </row>
     <row r="49" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="54">
+      <c r="A49" s="47">
         <v>45901</v>
       </c>
-      <c r="B49" s="55"/>
-      <c r="C49" s="55"/>
-      <c r="D49" s="55"/>
-      <c r="E49" s="55"/>
-      <c r="F49" s="55"/>
-      <c r="G49" s="55"/>
-      <c r="H49" s="55"/>
-      <c r="I49" s="55"/>
-      <c r="J49" s="55"/>
-      <c r="K49" s="55"/>
-      <c r="L49" s="55"/>
-      <c r="M49" s="55"/>
-      <c r="N49" s="55"/>
-      <c r="O49" s="56"/>
+      <c r="B49" s="48"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="48"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="48"/>
+      <c r="I49" s="48"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="48"/>
+      <c r="M49" s="48"/>
+      <c r="N49" s="48"/>
+      <c r="O49" s="49"/>
     </row>
     <row r="50" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
@@ -5030,19 +5027,19 @@
         <f>SUM(G51:G57)</f>
         <v>438</v>
       </c>
-      <c r="G58" s="57" t="s">
+      <c r="G58" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="58"/>
+      <c r="H58" s="51"/>
       <c r="I58" s="6">
         <f>SUM(I50:I57)</f>
         <v>35689</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="59" t="s">
+      <c r="K58" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L58" s="60"/>
+      <c r="L58" s="53"/>
       <c r="M58" s="7">
         <f>SUM(N50:N57)</f>
         <v>4186</v>
@@ -5056,23 +5053,23 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="54">
+      <c r="A59" s="47">
         <v>45931</v>
       </c>
-      <c r="B59" s="55"/>
-      <c r="C59" s="55"/>
-      <c r="D59" s="55"/>
-      <c r="E59" s="55"/>
-      <c r="F59" s="55"/>
-      <c r="G59" s="55"/>
-      <c r="H59" s="55"/>
-      <c r="I59" s="55"/>
-      <c r="J59" s="55"/>
-      <c r="K59" s="55"/>
-      <c r="L59" s="55"/>
-      <c r="M59" s="55"/>
-      <c r="N59" s="55"/>
-      <c r="O59" s="56"/>
+      <c r="B59" s="48"/>
+      <c r="C59" s="48"/>
+      <c r="D59" s="48"/>
+      <c r="E59" s="48"/>
+      <c r="F59" s="48"/>
+      <c r="G59" s="48"/>
+      <c r="H59" s="48"/>
+      <c r="I59" s="48"/>
+      <c r="J59" s="48"/>
+      <c r="K59" s="48"/>
+      <c r="L59" s="48"/>
+      <c r="M59" s="48"/>
+      <c r="N59" s="48"/>
+      <c r="O59" s="49"/>
     </row>
     <row r="60" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
@@ -5395,19 +5392,19 @@
         <f>SUM(G60:G66)</f>
         <v>640</v>
       </c>
-      <c r="G67" s="57" t="s">
+      <c r="G67" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="58"/>
+      <c r="H67" s="51"/>
       <c r="I67" s="6">
         <f>SUM(I60:I66)</f>
         <v>26988</v>
       </c>
       <c r="J67" s="5"/>
-      <c r="K67" s="59" t="s">
+      <c r="K67" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L67" s="60"/>
+      <c r="L67" s="53"/>
       <c r="M67" s="7">
         <f>SUM(N57:N66)</f>
         <v>0</v>
@@ -5421,23 +5418,23 @@
       </c>
     </row>
     <row r="68" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="54">
+      <c r="A68" s="47">
         <v>45962</v>
       </c>
-      <c r="B68" s="55"/>
-      <c r="C68" s="55"/>
-      <c r="D68" s="55"/>
-      <c r="E68" s="55"/>
-      <c r="F68" s="55"/>
-      <c r="G68" s="55"/>
-      <c r="H68" s="55"/>
-      <c r="I68" s="55"/>
-      <c r="J68" s="55"/>
-      <c r="K68" s="55"/>
-      <c r="L68" s="55"/>
-      <c r="M68" s="55"/>
-      <c r="N68" s="55"/>
-      <c r="O68" s="56"/>
+      <c r="B68" s="48"/>
+      <c r="C68" s="48"/>
+      <c r="D68" s="48"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="48"/>
+      <c r="G68" s="48"/>
+      <c r="H68" s="48"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="48"/>
+      <c r="K68" s="48"/>
+      <c r="L68" s="48"/>
+      <c r="M68" s="48"/>
+      <c r="N68" s="48"/>
+      <c r="O68" s="49"/>
     </row>
     <row r="69" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
@@ -6253,19 +6250,19 @@
         <f>SUM(G69:G80)</f>
         <v>3062</v>
       </c>
-      <c r="G87" s="57" t="s">
+      <c r="G87" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H87" s="58"/>
+      <c r="H87" s="51"/>
       <c r="I87" s="6">
         <f>SUM(I69:I86)</f>
         <v>123444</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="59" t="s">
+      <c r="K87" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L87" s="60"/>
+      <c r="L87" s="53"/>
       <c r="M87" s="7">
         <f>SUM(N69:N85)</f>
         <v>87602</v>
@@ -6279,23 +6276,23 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="54">
+      <c r="A88" s="47">
         <v>45992</v>
       </c>
-      <c r="B88" s="55"/>
-      <c r="C88" s="55"/>
-      <c r="D88" s="55"/>
-      <c r="E88" s="55"/>
-      <c r="F88" s="55"/>
-      <c r="G88" s="55"/>
-      <c r="H88" s="55"/>
-      <c r="I88" s="55"/>
-      <c r="J88" s="55"/>
-      <c r="K88" s="55"/>
-      <c r="L88" s="55"/>
-      <c r="M88" s="55"/>
-      <c r="N88" s="55"/>
-      <c r="O88" s="56"/>
+      <c r="B88" s="48"/>
+      <c r="C88" s="48"/>
+      <c r="D88" s="48"/>
+      <c r="E88" s="48"/>
+      <c r="F88" s="48"/>
+      <c r="G88" s="48"/>
+      <c r="H88" s="48"/>
+      <c r="I88" s="48"/>
+      <c r="J88" s="48"/>
+      <c r="K88" s="48"/>
+      <c r="L88" s="48"/>
+      <c r="M88" s="48"/>
+      <c r="N88" s="48"/>
+      <c r="O88" s="49"/>
     </row>
     <row r="89" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
@@ -6658,19 +6655,19 @@
         <f>SUM(G76:G87)</f>
         <v>4470</v>
       </c>
-      <c r="G97" s="57" t="s">
+      <c r="G97" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="58"/>
+      <c r="H97" s="51"/>
       <c r="I97" s="6">
         <f>SUM(I89:I96)</f>
         <v>27632</v>
       </c>
       <c r="J97" s="5"/>
-      <c r="K97" s="59" t="s">
+      <c r="K97" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L97" s="60"/>
+      <c r="L97" s="53"/>
       <c r="M97" s="7">
         <f>SUM(N89:N94)</f>
         <v>0</v>
@@ -6684,23 +6681,23 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="54">
+      <c r="A98" s="47">
         <v>46023</v>
       </c>
-      <c r="B98" s="55"/>
-      <c r="C98" s="55"/>
-      <c r="D98" s="55"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="55"/>
-      <c r="G98" s="55"/>
-      <c r="H98" s="55"/>
-      <c r="I98" s="55"/>
-      <c r="J98" s="55"/>
-      <c r="K98" s="55"/>
-      <c r="L98" s="55"/>
-      <c r="M98" s="55"/>
-      <c r="N98" s="55"/>
-      <c r="O98" s="56"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
+      <c r="L98" s="48"/>
+      <c r="M98" s="48"/>
+      <c r="N98" s="48"/>
+      <c r="O98" s="49"/>
     </row>
     <row r="99" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="38" t="s">
@@ -7724,19 +7721,19 @@
         <f>SUM(G106:G117)</f>
         <v>2483</v>
       </c>
-      <c r="G122" s="57" t="s">
+      <c r="G122" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H122" s="58"/>
+      <c r="H122" s="51"/>
       <c r="I122" s="6">
         <f>SUM(I99:I121)</f>
         <v>53972</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="59" t="s">
+      <c r="K122" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L122" s="60"/>
+      <c r="L122" s="53"/>
       <c r="M122" s="7">
         <f>SUM(N99:N121)</f>
         <v>30730</v>
@@ -7750,23 +7747,23 @@
       </c>
     </row>
     <row r="123" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="54">
+      <c r="A123" s="47">
         <v>46054</v>
       </c>
-      <c r="B123" s="55"/>
-      <c r="C123" s="55"/>
-      <c r="D123" s="55"/>
-      <c r="E123" s="55"/>
-      <c r="F123" s="55"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="55"/>
-      <c r="I123" s="55"/>
-      <c r="J123" s="55"/>
-      <c r="K123" s="55"/>
-      <c r="L123" s="55"/>
-      <c r="M123" s="55"/>
-      <c r="N123" s="55"/>
-      <c r="O123" s="56"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="48"/>
+      <c r="D123" s="48"/>
+      <c r="E123" s="48"/>
+      <c r="F123" s="48"/>
+      <c r="G123" s="48"/>
+      <c r="H123" s="48"/>
+      <c r="I123" s="48"/>
+      <c r="J123" s="48"/>
+      <c r="K123" s="48"/>
+      <c r="L123" s="48"/>
+      <c r="M123" s="48"/>
+      <c r="N123" s="48"/>
+      <c r="O123" s="49"/>
     </row>
     <row r="124" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
@@ -7906,19 +7903,19 @@
         <f>SUM(G110:G121)</f>
         <v>2121</v>
       </c>
-      <c r="G127" s="57" t="s">
+      <c r="G127" s="50" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="58"/>
+      <c r="H127" s="51"/>
       <c r="I127" s="6">
         <f>SUM(I124:I126)</f>
         <v>6587</v>
       </c>
       <c r="J127" s="5"/>
-      <c r="K127" s="59" t="s">
+      <c r="K127" s="52" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="60"/>
+      <c r="L127" s="53"/>
       <c r="M127" s="7">
         <f>SUM(N124:N125)</f>
         <v>0</v>
@@ -7932,23 +7929,23 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="54">
+      <c r="A128" s="47">
         <v>46082</v>
       </c>
-      <c r="B128" s="55"/>
-      <c r="C128" s="55"/>
-      <c r="D128" s="55"/>
-      <c r="E128" s="55"/>
-      <c r="F128" s="55"/>
-      <c r="G128" s="55"/>
-      <c r="H128" s="55"/>
-      <c r="I128" s="55"/>
-      <c r="J128" s="55"/>
-      <c r="K128" s="55"/>
-      <c r="L128" s="55"/>
-      <c r="M128" s="55"/>
-      <c r="N128" s="55"/>
-      <c r="O128" s="56"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="48"/>
+      <c r="D128" s="48"/>
+      <c r="E128" s="48"/>
+      <c r="F128" s="48"/>
+      <c r="G128" s="48"/>
+      <c r="H128" s="48"/>
+      <c r="I128" s="48"/>
+      <c r="J128" s="48"/>
+      <c r="K128" s="48"/>
+      <c r="L128" s="48"/>
+      <c r="M128" s="48"/>
+      <c r="N128" s="48"/>
+      <c r="O128" s="49"/>
     </row>
     <row r="129" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
@@ -8111,7 +8108,7 @@
         <v>59</v>
       </c>
       <c r="K132" s="1" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="L132" s="2">
         <v>3.6</v>
@@ -8124,45 +8121,82 @@
     </row>
     <row r="133" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C133" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="D133" s="2">
+        <v>15076731826</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="G133" s="2">
+        <v>0</v>
+      </c>
+      <c r="H133" s="2">
+        <v>0</v>
+      </c>
+      <c r="I133" s="9">
+        <v>3198</v>
+      </c>
+      <c r="J133" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K133" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L133" s="1">
+        <v>3.27</v>
+      </c>
+      <c r="M133" s="1"/>
+      <c r="N133" s="3"/>
+    </row>
+    <row r="134" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A134" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C134" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="D134" s="2">
+        <v>13894399600</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F134" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="B133" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="C133" s="2">
-        <v>3.8</v>
-      </c>
-      <c r="D133" s="2">
-        <v>15577119500</v>
-      </c>
-      <c r="E133" s="43" t="s">
-        <v>430</v>
-      </c>
-      <c r="F133" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="G133" s="2">
-        <v>800</v>
-      </c>
-      <c r="H133" s="2">
-        <v>1060</v>
-      </c>
-      <c r="I133" s="9">
-        <v>1860</v>
-      </c>
-      <c r="J133" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K133" s="1" t="s">
+      <c r="G134" s="2">
+        <v>0</v>
+      </c>
+      <c r="H134" s="2">
+        <v>0</v>
+      </c>
+      <c r="I134" s="9">
+        <v>2179</v>
+      </c>
+      <c r="J134" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K134" s="1" t="s">
         <v>412</v>
       </c>
-      <c r="L133" s="2">
-        <v>3.11</v>
-      </c>
-      <c r="N133" s="17"/>
-    </row>
-    <row r="134" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I134" s="9"/>
+      <c r="L134" s="2">
+        <v>3.27</v>
+      </c>
+      <c r="M134" s="1"/>
       <c r="N134" s="17"/>
     </row>
     <row r="135" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
@@ -8623,25 +8657,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="A128:O128"/>
-    <mergeCell ref="G127:H127"/>
-    <mergeCell ref="K127:L127"/>
-    <mergeCell ref="A98:O98"/>
-    <mergeCell ref="G97:H97"/>
-    <mergeCell ref="K97:L97"/>
-    <mergeCell ref="A123:O123"/>
-    <mergeCell ref="G122:H122"/>
-    <mergeCell ref="K122:L122"/>
-    <mergeCell ref="A27:O27"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A68:O68"/>
-    <mergeCell ref="K67:L67"/>
-    <mergeCell ref="G58:H58"/>
-    <mergeCell ref="K58:L58"/>
-    <mergeCell ref="G48:H48"/>
-    <mergeCell ref="A59:O59"/>
-    <mergeCell ref="G67:H67"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="F2:K2"/>
     <mergeCell ref="L2:O2"/>
@@ -8658,6 +8673,25 @@
     <mergeCell ref="K87:L87"/>
     <mergeCell ref="K48:L48"/>
     <mergeCell ref="A49:O49"/>
+    <mergeCell ref="A27:O27"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A68:O68"/>
+    <mergeCell ref="K67:L67"/>
+    <mergeCell ref="G58:H58"/>
+    <mergeCell ref="K58:L58"/>
+    <mergeCell ref="G48:H48"/>
+    <mergeCell ref="A59:O59"/>
+    <mergeCell ref="G67:H67"/>
+    <mergeCell ref="A128:O128"/>
+    <mergeCell ref="G127:H127"/>
+    <mergeCell ref="K127:L127"/>
+    <mergeCell ref="A98:O98"/>
+    <mergeCell ref="G97:H97"/>
+    <mergeCell ref="K97:L97"/>
+    <mergeCell ref="A123:O123"/>
+    <mergeCell ref="G122:H122"/>
+    <mergeCell ref="K122:L122"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/业绩表/业绩表.xlsx
+++ b/业绩表/业绩表.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github本地\github\业绩表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF98D37-21EF-4C5D-BBAE-1635E4FDD022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D6E3A44-DA7E-42F0-B589-FBD90262BDD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2520" yWindow="1695" windowWidth="19095" windowHeight="12030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$249</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="881" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="462">
   <si>
     <t>姓名</t>
   </si>
@@ -1663,6 +1663,118 @@
   <si>
     <t>参蛾温肾口服液*10 无事牌*2 五虫通脉液*2</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">药都滋补膏*7 太合地户灸*15 天柱通阳灸*5 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF0229741118450</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF5125880163761</t>
+  </si>
+  <si>
+    <t>耿忠诚</t>
+  </si>
+  <si>
+    <t>耿忠诚</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>陕西省西安市 长安区郭杜东街49号樱花西岸小区</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>益寿强身膏*20盒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF5139998072591</t>
+  </si>
+  <si>
+    <t>SF0229941741278</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太合地户灸*10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>329399256784</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>329392967546</t>
+  </si>
+  <si>
+    <t>329399256572</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>史铁钢</t>
+  </si>
+  <si>
+    <t>史铁钢</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>转介绍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>河南省漯河市临颍县樊城回族镇夏庄村26号</t>
+  </si>
+  <si>
+    <t>太和地户灸*10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">天柱通阳灸*15 太合地户灸*5 </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天柱通阳灸*20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>天通就*10</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>孙</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>杨艳（刘政委转介绍</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>太合地户灸*20</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>SF5139980464507</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>329405433264</t>
+  </si>
+  <si>
+    <t>周林</t>
+  </si>
+  <si>
+    <t>玉麒麟</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>浙江省嘉兴市放鹤洲花园77栋301室</t>
+  </si>
+  <si>
+    <t>参蛾温肾口服液*5玖玖心宝*1五虫通脉液*1</t>
+  </si>
+  <si>
+    <t>SF5192263183816</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +2106,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2136,13 +2248,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2155,6 +2261,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="57" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2176,6 +2291,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2658,7 +2776,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q250"/>
+  <dimension ref="A1:Q249"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="42" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.875" style="2" customWidth="1"/>
@@ -2730,48 +2848,48 @@
       <c r="Q1" s="19"/>
     </row>
     <row r="2" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="55" t="s">
         <v>151</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="56" t="s">
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57" t="s">
         <v>369</v>
       </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="57"/>
-      <c r="K2" s="57"/>
-      <c r="L2" s="58" t="s">
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="59" t="s">
         <v>370</v>
       </c>
-      <c r="M2" s="59"/>
-      <c r="N2" s="59"/>
-      <c r="O2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="61"/>
       <c r="P2" s="35"/>
       <c r="Q2" s="35"/>
     </row>
     <row r="3" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="47">
+      <c r="A3" s="52">
         <v>45748</v>
       </c>
-      <c r="B3" s="48"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="48"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="49"/>
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="54"/>
     </row>
     <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="1" t="s">
@@ -2865,23 +2983,23 @@
       <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="47">
+      <c r="A6" s="52">
         <v>45778</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-      <c r="L6" s="48"/>
-      <c r="M6" s="48"/>
-      <c r="N6" s="48"/>
-      <c r="O6" s="49"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
+      <c r="K6" s="53"/>
+      <c r="L6" s="53"/>
+      <c r="M6" s="53"/>
+      <c r="N6" s="53"/>
+      <c r="O6" s="54"/>
       <c r="P6" s="23"/>
       <c r="Q6" s="22"/>
     </row>
@@ -3213,19 +3331,19 @@
       <c r="D14" s="5"/>
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H14" s="51"/>
+      <c r="H14" s="49"/>
       <c r="I14" s="6">
         <f>SUM(I7:I13)</f>
         <v>32768</v>
       </c>
       <c r="J14" s="5"/>
-      <c r="K14" s="52" t="s">
+      <c r="K14" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L14" s="53"/>
+      <c r="L14" s="51"/>
       <c r="M14" s="7">
         <f>SUM(N7:N13)</f>
         <v>6500</v>
@@ -3241,23 +3359,23 @@
       <c r="Q14" s="22"/>
     </row>
     <row r="15" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="47">
+      <c r="A15" s="52">
         <v>45809</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="48"/>
-      <c r="E15" s="48"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="48"/>
-      <c r="M15" s="48"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="49"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
+      <c r="J15" s="53"/>
+      <c r="K15" s="53"/>
+      <c r="L15" s="53"/>
+      <c r="M15" s="53"/>
+      <c r="N15" s="53"/>
+      <c r="O15" s="54"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="22"/>
     </row>
@@ -3710,19 +3828,19 @@
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
-      <c r="G26" s="50" t="s">
+      <c r="G26" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H26" s="51"/>
+      <c r="H26" s="49"/>
       <c r="I26" s="6">
         <f>SUM(I16:I25)</f>
         <v>47760</v>
       </c>
       <c r="J26" s="5"/>
-      <c r="K26" s="52" t="s">
+      <c r="K26" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L26" s="53"/>
+      <c r="L26" s="51"/>
       <c r="M26" s="7">
         <f>SUM(N18:N25)</f>
         <v>0</v>
@@ -3736,23 +3854,23 @@
       </c>
     </row>
     <row r="27" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="47">
+      <c r="A27" s="52">
         <v>45839</v>
       </c>
-      <c r="B27" s="48"/>
-      <c r="C27" s="48"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="48"/>
-      <c r="H27" s="48"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="48"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="49"/>
+      <c r="B27" s="53"/>
+      <c r="C27" s="53"/>
+      <c r="D27" s="53"/>
+      <c r="E27" s="53"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="53"/>
+      <c r="H27" s="53"/>
+      <c r="I27" s="53"/>
+      <c r="J27" s="53"/>
+      <c r="K27" s="53"/>
+      <c r="L27" s="53"/>
+      <c r="M27" s="53"/>
+      <c r="N27" s="53"/>
+      <c r="O27" s="54"/>
     </row>
     <row r="28" spans="1:17" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1" t="s">
@@ -4382,19 +4500,19 @@
         <f>G33+G35+G37+G40</f>
         <v>0</v>
       </c>
-      <c r="G42" s="50" t="s">
+      <c r="G42" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H42" s="51"/>
+      <c r="H42" s="49"/>
       <c r="I42" s="6">
         <f>SUM(I28:I41)</f>
         <v>52960</v>
       </c>
       <c r="J42" s="5"/>
-      <c r="K42" s="52" t="s">
+      <c r="K42" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L42" s="53"/>
+      <c r="L42" s="51"/>
       <c r="M42" s="7">
         <f>SUM(N28:N41)</f>
         <v>18470</v>
@@ -4408,23 +4526,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="47">
+      <c r="A43" s="52">
         <v>45870</v>
       </c>
-      <c r="B43" s="48"/>
-      <c r="C43" s="48"/>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="48"/>
-      <c r="J43" s="48"/>
-      <c r="K43" s="48"/>
-      <c r="L43" s="48"/>
-      <c r="M43" s="48"/>
-      <c r="N43" s="48"/>
-      <c r="O43" s="49"/>
+      <c r="B43" s="53"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="53"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="53"/>
+      <c r="H43" s="53"/>
+      <c r="I43" s="53"/>
+      <c r="J43" s="53"/>
+      <c r="K43" s="53"/>
+      <c r="L43" s="53"/>
+      <c r="M43" s="53"/>
+      <c r="N43" s="53"/>
+      <c r="O43" s="54"/>
     </row>
     <row r="44" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="36" t="s">
@@ -4612,19 +4730,19 @@
         <f>G46+G47</f>
         <v>585</v>
       </c>
-      <c r="G48" s="50" t="s">
+      <c r="G48" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H48" s="51"/>
+      <c r="H48" s="49"/>
       <c r="I48" s="6">
         <f>SUM(I44:I47)</f>
         <v>11470</v>
       </c>
       <c r="J48" s="5"/>
-      <c r="K48" s="52" t="s">
+      <c r="K48" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L48" s="53"/>
+      <c r="L48" s="51"/>
       <c r="M48" s="7">
         <f>SUM(N44:N47)</f>
         <v>2985</v>
@@ -4638,23 +4756,23 @@
       </c>
     </row>
     <row r="49" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="47">
+      <c r="A49" s="52">
         <v>45901</v>
       </c>
-      <c r="B49" s="48"/>
-      <c r="C49" s="48"/>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
-      <c r="I49" s="48"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="48"/>
-      <c r="N49" s="48"/>
-      <c r="O49" s="49"/>
+      <c r="B49" s="53"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="53"/>
+      <c r="K49" s="53"/>
+      <c r="L49" s="53"/>
+      <c r="M49" s="53"/>
+      <c r="N49" s="53"/>
+      <c r="O49" s="54"/>
     </row>
     <row r="50" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1" t="s">
@@ -5027,19 +5145,19 @@
         <f>SUM(G51:G57)</f>
         <v>438</v>
       </c>
-      <c r="G58" s="50" t="s">
+      <c r="G58" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H58" s="51"/>
+      <c r="H58" s="49"/>
       <c r="I58" s="6">
         <f>SUM(I50:I57)</f>
         <v>35689</v>
       </c>
       <c r="J58" s="5"/>
-      <c r="K58" s="52" t="s">
+      <c r="K58" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L58" s="53"/>
+      <c r="L58" s="51"/>
       <c r="M58" s="7">
         <f>SUM(N50:N57)</f>
         <v>4186</v>
@@ -5053,23 +5171,23 @@
       </c>
     </row>
     <row r="59" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="47">
+      <c r="A59" s="52">
         <v>45931</v>
       </c>
-      <c r="B59" s="48"/>
-      <c r="C59" s="48"/>
-      <c r="D59" s="48"/>
-      <c r="E59" s="48"/>
-      <c r="F59" s="48"/>
-      <c r="G59" s="48"/>
-      <c r="H59" s="48"/>
-      <c r="I59" s="48"/>
-      <c r="J59" s="48"/>
-      <c r="K59" s="48"/>
-      <c r="L59" s="48"/>
-      <c r="M59" s="48"/>
-      <c r="N59" s="48"/>
-      <c r="O59" s="49"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="53"/>
+      <c r="K59" s="53"/>
+      <c r="L59" s="53"/>
+      <c r="M59" s="53"/>
+      <c r="N59" s="53"/>
+      <c r="O59" s="54"/>
     </row>
     <row r="60" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1" t="s">
@@ -5392,19 +5510,19 @@
         <f>SUM(G60:G66)</f>
         <v>640</v>
       </c>
-      <c r="G67" s="50" t="s">
+      <c r="G67" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H67" s="51"/>
+      <c r="H67" s="49"/>
       <c r="I67" s="6">
         <f>SUM(I60:I66)</f>
         <v>26988</v>
       </c>
       <c r="J67" s="5"/>
-      <c r="K67" s="52" t="s">
+      <c r="K67" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L67" s="53"/>
+      <c r="L67" s="51"/>
       <c r="M67" s="7">
         <f>SUM(N57:N66)</f>
         <v>0</v>
@@ -5418,23 +5536,23 @@
       </c>
     </row>
     <row r="68" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="47">
+      <c r="A68" s="52">
         <v>45962</v>
       </c>
-      <c r="B68" s="48"/>
-      <c r="C68" s="48"/>
-      <c r="D68" s="48"/>
-      <c r="E68" s="48"/>
-      <c r="F68" s="48"/>
-      <c r="G68" s="48"/>
-      <c r="H68" s="48"/>
-      <c r="I68" s="48"/>
-      <c r="J68" s="48"/>
-      <c r="K68" s="48"/>
-      <c r="L68" s="48"/>
-      <c r="M68" s="48"/>
-      <c r="N68" s="48"/>
-      <c r="O68" s="49"/>
+      <c r="B68" s="53"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+      <c r="K68" s="53"/>
+      <c r="L68" s="53"/>
+      <c r="M68" s="53"/>
+      <c r="N68" s="53"/>
+      <c r="O68" s="54"/>
     </row>
     <row r="69" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="1" t="s">
@@ -6250,19 +6368,19 @@
         <f>SUM(G69:G80)</f>
         <v>3062</v>
       </c>
-      <c r="G87" s="50" t="s">
+      <c r="G87" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H87" s="51"/>
+      <c r="H87" s="49"/>
       <c r="I87" s="6">
         <f>SUM(I69:I86)</f>
         <v>123444</v>
       </c>
       <c r="J87" s="5"/>
-      <c r="K87" s="52" t="s">
+      <c r="K87" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L87" s="53"/>
+      <c r="L87" s="51"/>
       <c r="M87" s="7">
         <f>SUM(N69:N85)</f>
         <v>87602</v>
@@ -6276,23 +6394,23 @@
       </c>
     </row>
     <row r="88" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="47">
+      <c r="A88" s="52">
         <v>45992</v>
       </c>
-      <c r="B88" s="48"/>
-      <c r="C88" s="48"/>
-      <c r="D88" s="48"/>
-      <c r="E88" s="48"/>
-      <c r="F88" s="48"/>
-      <c r="G88" s="48"/>
-      <c r="H88" s="48"/>
-      <c r="I88" s="48"/>
-      <c r="J88" s="48"/>
-      <c r="K88" s="48"/>
-      <c r="L88" s="48"/>
-      <c r="M88" s="48"/>
-      <c r="N88" s="48"/>
-      <c r="O88" s="49"/>
+      <c r="B88" s="53"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="53"/>
+      <c r="K88" s="53"/>
+      <c r="L88" s="53"/>
+      <c r="M88" s="53"/>
+      <c r="N88" s="53"/>
+      <c r="O88" s="54"/>
     </row>
     <row r="89" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="1" t="s">
@@ -6655,19 +6773,19 @@
         <f>SUM(G76:G87)</f>
         <v>4470</v>
       </c>
-      <c r="G97" s="50" t="s">
+      <c r="G97" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H97" s="51"/>
+      <c r="H97" s="49"/>
       <c r="I97" s="6">
         <f>SUM(I89:I96)</f>
         <v>27632</v>
       </c>
       <c r="J97" s="5"/>
-      <c r="K97" s="52" t="s">
+      <c r="K97" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L97" s="53"/>
+      <c r="L97" s="51"/>
       <c r="M97" s="7">
         <f>SUM(N89:N94)</f>
         <v>0</v>
@@ -6681,23 +6799,23 @@
       </c>
     </row>
     <row r="98" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A98" s="47">
+      <c r="A98" s="52">
         <v>46023</v>
       </c>
-      <c r="B98" s="48"/>
-      <c r="C98" s="48"/>
-      <c r="D98" s="48"/>
-      <c r="E98" s="48"/>
-      <c r="F98" s="48"/>
-      <c r="G98" s="48"/>
-      <c r="H98" s="48"/>
-      <c r="I98" s="48"/>
-      <c r="J98" s="48"/>
-      <c r="K98" s="48"/>
-      <c r="L98" s="48"/>
-      <c r="M98" s="48"/>
-      <c r="N98" s="48"/>
-      <c r="O98" s="49"/>
+      <c r="B98" s="53"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="53"/>
+      <c r="J98" s="53"/>
+      <c r="K98" s="53"/>
+      <c r="L98" s="53"/>
+      <c r="M98" s="53"/>
+      <c r="N98" s="53"/>
+      <c r="O98" s="54"/>
     </row>
     <row r="99" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="38" t="s">
@@ -7721,19 +7839,19 @@
         <f>SUM(G106:G117)</f>
         <v>2483</v>
       </c>
-      <c r="G122" s="50" t="s">
+      <c r="G122" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H122" s="51"/>
+      <c r="H122" s="49"/>
       <c r="I122" s="6">
         <f>SUM(I99:I121)</f>
         <v>53972</v>
       </c>
       <c r="J122" s="5"/>
-      <c r="K122" s="52" t="s">
+      <c r="K122" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L122" s="53"/>
+      <c r="L122" s="51"/>
       <c r="M122" s="7">
         <f>SUM(N99:N121)</f>
         <v>30730</v>
@@ -7747,23 +7865,23 @@
       </c>
     </row>
     <row r="123" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A123" s="47">
+      <c r="A123" s="52">
         <v>46054</v>
       </c>
-      <c r="B123" s="48"/>
-      <c r="C123" s="48"/>
-      <c r="D123" s="48"/>
-      <c r="E123" s="48"/>
-      <c r="F123" s="48"/>
-      <c r="G123" s="48"/>
-      <c r="H123" s="48"/>
-      <c r="I123" s="48"/>
-      <c r="J123" s="48"/>
-      <c r="K123" s="48"/>
-      <c r="L123" s="48"/>
-      <c r="M123" s="48"/>
-      <c r="N123" s="48"/>
-      <c r="O123" s="49"/>
+      <c r="B123" s="53"/>
+      <c r="C123" s="53"/>
+      <c r="D123" s="53"/>
+      <c r="E123" s="53"/>
+      <c r="F123" s="53"/>
+      <c r="G123" s="53"/>
+      <c r="H123" s="53"/>
+      <c r="I123" s="53"/>
+      <c r="J123" s="53"/>
+      <c r="K123" s="53"/>
+      <c r="L123" s="53"/>
+      <c r="M123" s="53"/>
+      <c r="N123" s="53"/>
+      <c r="O123" s="54"/>
     </row>
     <row r="124" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
@@ -7903,19 +8021,19 @@
         <f>SUM(G110:G121)</f>
         <v>2121</v>
       </c>
-      <c r="G127" s="50" t="s">
+      <c r="G127" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="H127" s="51"/>
+      <c r="H127" s="49"/>
       <c r="I127" s="6">
         <f>SUM(I124:I126)</f>
         <v>6587</v>
       </c>
       <c r="J127" s="5"/>
-      <c r="K127" s="52" t="s">
+      <c r="K127" s="50" t="s">
         <v>64</v>
       </c>
-      <c r="L127" s="53"/>
+      <c r="L127" s="51"/>
       <c r="M127" s="7">
         <f>SUM(N124:N125)</f>
         <v>0</v>
@@ -7929,23 +8047,23 @@
       </c>
     </row>
     <row r="128" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A128" s="47">
+      <c r="A128" s="52">
         <v>46082</v>
       </c>
-      <c r="B128" s="48"/>
-      <c r="C128" s="48"/>
-      <c r="D128" s="48"/>
-      <c r="E128" s="48"/>
-      <c r="F128" s="48"/>
-      <c r="G128" s="48"/>
-      <c r="H128" s="48"/>
-      <c r="I128" s="48"/>
-      <c r="J128" s="48"/>
-      <c r="K128" s="48"/>
-      <c r="L128" s="48"/>
-      <c r="M128" s="48"/>
-      <c r="N128" s="48"/>
-      <c r="O128" s="49"/>
+      <c r="B128" s="53"/>
+      <c r="C128" s="53"/>
+      <c r="D128" s="53"/>
+      <c r="E128" s="53"/>
+      <c r="F128" s="53"/>
+      <c r="G128" s="53"/>
+      <c r="H128" s="53"/>
+      <c r="I128" s="53"/>
+      <c r="J128" s="53"/>
+      <c r="K128" s="53"/>
+      <c r="L128" s="53"/>
+      <c r="M128" s="53"/>
+      <c r="N128" s="53"/>
+      <c r="O128" s="54"/>
     </row>
     <row r="129" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="1" t="s">
@@ -8084,7 +8202,7 @@
         <v>182</v>
       </c>
       <c r="C132" s="2">
-        <v>9.5</v>
+        <v>12.4</v>
       </c>
       <c r="D132" s="2">
         <v>13624833466</v>
@@ -8156,8 +8274,10 @@
       <c r="L133" s="1">
         <v>3.27</v>
       </c>
-      <c r="M133" s="1"/>
-      <c r="N133" s="3"/>
+      <c r="M133" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="N133" s="17"/>
     </row>
     <row r="134" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="1" t="s">
@@ -8191,115 +8311,581 @@
         <v>59</v>
       </c>
       <c r="K134" s="1" t="s">
-        <v>412</v>
+        <v>58</v>
       </c>
       <c r="L134" s="2">
         <v>3.27</v>
       </c>
-      <c r="M134" s="1"/>
+      <c r="M134" s="1" t="s">
+        <v>433</v>
+      </c>
       <c r="N134" s="17"/>
     </row>
     <row r="135" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I135" s="9"/>
-      <c r="N135" s="17"/>
+      <c r="A135" s="5"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="5"/>
+      <c r="D135" s="5"/>
+      <c r="E135" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F135" s="20">
+        <f>SUM(G118:G129)</f>
+        <v>2296</v>
+      </c>
+      <c r="G135" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H135" s="49"/>
+      <c r="I135" s="6">
+        <f>SUM(I129:I134)</f>
+        <v>14019</v>
+      </c>
+      <c r="J135" s="5"/>
+      <c r="K135" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="L135" s="51"/>
+      <c r="M135" s="7">
+        <f>SUM(N132:N133)</f>
+        <v>0</v>
+      </c>
+      <c r="N135" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O135" s="8">
+        <f>I135-M135</f>
+        <v>14019</v>
+      </c>
     </row>
     <row r="136" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I136" s="9"/>
-      <c r="N136" s="17"/>
+      <c r="A136" s="52">
+        <v>46113</v>
+      </c>
+      <c r="B136" s="53"/>
+      <c r="C136" s="53"/>
+      <c r="D136" s="53"/>
+      <c r="E136" s="53"/>
+      <c r="F136" s="53"/>
+      <c r="G136" s="53"/>
+      <c r="H136" s="53"/>
+      <c r="I136" s="53"/>
+      <c r="J136" s="53"/>
+      <c r="K136" s="53"/>
+      <c r="L136" s="53"/>
+      <c r="M136" s="53"/>
+      <c r="N136" s="53"/>
+      <c r="O136" s="54"/>
     </row>
     <row r="137" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I137" s="9"/>
+      <c r="A137" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C137" s="13">
+        <v>12.1</v>
+      </c>
+      <c r="D137" s="2">
+        <v>17721447449</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="G137" s="2">
+        <v>0</v>
+      </c>
+      <c r="H137" s="2">
+        <v>0</v>
+      </c>
+      <c r="I137" s="9">
+        <v>2089</v>
+      </c>
+      <c r="J137" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K137" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L137" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M137" s="1" t="s">
+        <v>439</v>
+      </c>
       <c r="N137" s="17"/>
     </row>
     <row r="138" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I138" s="9"/>
+      <c r="A138" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="C138" s="2">
+        <v>3.28</v>
+      </c>
+      <c r="D138" s="2">
+        <v>18191556283</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="G138" s="2">
+        <v>0</v>
+      </c>
+      <c r="H138" s="2">
+        <v>0</v>
+      </c>
+      <c r="I138" s="9">
+        <v>11960</v>
+      </c>
+      <c r="J138" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L138" s="2">
+        <v>4.5</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>438</v>
+      </c>
       <c r="N138" s="17"/>
+      <c r="O138" s="1" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="139" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I139" s="9"/>
+      <c r="A139" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="C139" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="D139" s="2">
+        <v>13624833466</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G139" s="2">
+        <v>0</v>
+      </c>
+      <c r="H139" s="2">
+        <v>0</v>
+      </c>
+      <c r="I139" s="9">
+        <v>199</v>
+      </c>
+      <c r="J139" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K139" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L139" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M139" s="47" t="s">
+        <v>443</v>
+      </c>
       <c r="N139" s="17"/>
     </row>
     <row r="140" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I140" s="9"/>
+      <c r="A140" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C140" s="2">
+        <v>12.21</v>
+      </c>
+      <c r="D140" s="2">
+        <v>13008114373</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="G140" s="2">
+        <v>0</v>
+      </c>
+      <c r="H140" s="2">
+        <v>0</v>
+      </c>
+      <c r="I140" s="9">
+        <v>199</v>
+      </c>
+      <c r="J140" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K140" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L140" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M140" s="47" t="s">
+        <v>442</v>
+      </c>
       <c r="N140" s="17"/>
     </row>
     <row r="141" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I141" s="9"/>
+      <c r="A141" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="D141" s="2">
+        <v>15713954632</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="G141" s="2">
+        <v>0</v>
+      </c>
+      <c r="H141" s="2">
+        <v>0</v>
+      </c>
+      <c r="I141" s="9">
+        <v>199</v>
+      </c>
+      <c r="J141" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K141" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="L141" s="2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="M141" s="47" t="s">
+        <v>441</v>
+      </c>
       <c r="N141" s="17"/>
+      <c r="O141" s="1" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="142" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I142" s="9"/>
+      <c r="A142" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C142" s="13">
+        <v>12.1</v>
+      </c>
+      <c r="D142" s="2">
+        <v>17721447449</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G142" s="2">
+        <v>0</v>
+      </c>
+      <c r="H142" s="2">
+        <v>0</v>
+      </c>
+      <c r="I142" s="9">
+        <v>396</v>
+      </c>
+      <c r="J142" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K142" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L142" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M142" s="1"/>
       <c r="N142" s="17"/>
     </row>
     <row r="143" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I143" s="9"/>
+      <c r="A143" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C143" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="D143" s="2">
+        <v>13936291792</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="G143" s="2">
+        <v>0</v>
+      </c>
+      <c r="H143" s="2">
+        <v>0</v>
+      </c>
+      <c r="I143" s="9">
+        <v>398</v>
+      </c>
+      <c r="J143" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K143" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L143" s="14">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M143" s="62" t="s">
+        <v>456</v>
+      </c>
       <c r="N143" s="17"/>
     </row>
     <row r="144" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I144" s="9"/>
+      <c r="A144" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="C144" s="2">
+        <v>12.21</v>
+      </c>
+      <c r="D144" s="2">
+        <v>13008114373</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="G144" s="2">
+        <v>0</v>
+      </c>
+      <c r="H144" s="2">
+        <v>0</v>
+      </c>
+      <c r="I144" s="9">
+        <v>198</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K144" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L144" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="M144" s="1"/>
       <c r="N144" s="17"/>
-    </row>
-    <row r="145" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I145" s="9"/>
+      <c r="O144" s="12"/>
+    </row>
+    <row r="145" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A145" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="B145" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="C145" s="2">
+        <v>12.4</v>
+      </c>
+      <c r="D145" s="2">
+        <v>13894399600</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="G145" s="2">
+        <v>0</v>
+      </c>
+      <c r="H145" s="2">
+        <v>0</v>
+      </c>
+      <c r="I145" s="9">
+        <v>398</v>
+      </c>
+      <c r="J145" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="L145" s="2">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>455</v>
+      </c>
       <c r="N145" s="17"/>
     </row>
-    <row r="146" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I146" s="9"/>
+    <row r="146" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A146" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C146" s="2">
+        <v>3.8</v>
+      </c>
+      <c r="D146" s="2">
+        <v>13586479193</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="G146" s="2">
+        <v>0</v>
+      </c>
+      <c r="H146" s="2">
+        <v>0</v>
+      </c>
+      <c r="I146" s="9">
+        <v>1599</v>
+      </c>
+      <c r="J146" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K146" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="L146" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>461</v>
+      </c>
       <c r="N146" s="17"/>
     </row>
-    <row r="147" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I147" s="9"/>
       <c r="N147" s="17"/>
     </row>
-    <row r="148" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I148" s="9"/>
-      <c r="N148" s="17"/>
-    </row>
-    <row r="149" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A148" s="5"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="5"/>
+      <c r="D148" s="5"/>
+      <c r="E148" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="F148" s="20">
+        <f>SUM(G130:G141)</f>
+        <v>484</v>
+      </c>
+      <c r="G148" s="48" t="s">
+        <v>45</v>
+      </c>
+      <c r="H148" s="49"/>
+      <c r="I148" s="6">
+        <f>SUM(I137:I146)</f>
+        <v>17635</v>
+      </c>
+      <c r="J148" s="5"/>
+      <c r="K148" s="50" t="s">
+        <v>64</v>
+      </c>
+      <c r="L148" s="51"/>
+      <c r="M148" s="7">
+        <f>SUM(M144:M144)</f>
+        <v>0</v>
+      </c>
+      <c r="N148" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="O148" s="8">
+        <f>I148-M148</f>
+        <v>17635</v>
+      </c>
+    </row>
+    <row r="149" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I149" s="9"/>
       <c r="N149" s="17"/>
     </row>
-    <row r="150" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I150" s="9"/>
       <c r="N150" s="17"/>
     </row>
-    <row r="151" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I151" s="9"/>
       <c r="N151" s="17"/>
     </row>
-    <row r="152" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I152" s="9"/>
       <c r="N152" s="17"/>
     </row>
-    <row r="153" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I153" s="9"/>
       <c r="N153" s="17"/>
     </row>
-    <row r="154" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I154" s="9"/>
       <c r="N154" s="17"/>
     </row>
-    <row r="155" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I155" s="9"/>
       <c r="N155" s="17"/>
     </row>
-    <row r="156" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I156" s="9"/>
       <c r="N156" s="17"/>
     </row>
-    <row r="157" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I157" s="9"/>
       <c r="N157" s="17"/>
     </row>
-    <row r="158" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I158" s="9"/>
       <c r="N158" s="17"/>
     </row>
-    <row r="159" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I159" s="9"/>
       <c r="N159" s="17"/>
     </row>
-    <row r="160" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="I160" s="9"/>
       <c r="N160" s="17"/>
     </row>
@@ -8628,7 +9214,6 @@
       <c r="N241" s="17"/>
     </row>
     <row r="242" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="I242" s="9"/>
       <c r="N242" s="17"/>
     </row>
     <row r="243" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
@@ -8652,14 +9237,8 @@
     <row r="249" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="N249" s="17"/>
     </row>
-    <row r="250" spans="9:14" ht="42" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="N250" s="17"/>
-    </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="F2:K2"/>
-    <mergeCell ref="L2:O2"/>
+  <mergeCells count="40">
     <mergeCell ref="A88:O88"/>
     <mergeCell ref="A3:O3"/>
     <mergeCell ref="A6:O6"/>
@@ -8671,11 +9250,12 @@
     <mergeCell ref="K42:L42"/>
     <mergeCell ref="G87:H87"/>
     <mergeCell ref="K87:L87"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="A49:O49"/>
     <mergeCell ref="A27:O27"/>
     <mergeCell ref="G26:H26"/>
     <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="F2:K2"/>
+    <mergeCell ref="L2:O2"/>
     <mergeCell ref="A68:O68"/>
     <mergeCell ref="K67:L67"/>
     <mergeCell ref="G58:H58"/>
@@ -8683,6 +9263,8 @@
     <mergeCell ref="G48:H48"/>
     <mergeCell ref="A59:O59"/>
     <mergeCell ref="G67:H67"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="A49:O49"/>
     <mergeCell ref="A128:O128"/>
     <mergeCell ref="G127:H127"/>
     <mergeCell ref="K127:L127"/>
@@ -8692,6 +9274,11 @@
     <mergeCell ref="A123:O123"/>
     <mergeCell ref="G122:H122"/>
     <mergeCell ref="K122:L122"/>
+    <mergeCell ref="G148:H148"/>
+    <mergeCell ref="K148:L148"/>
+    <mergeCell ref="G135:H135"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="A136:O136"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
